--- a/research/traditional_assets/database/data/austria/austria_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_software_system_application.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1079689613831751</v>
+        <v>0.1077440358758555</v>
       </c>
       <c r="C2">
-        <v>192.8890355854674</v>
+        <v>191.5499228732276</v>
       </c>
       <c r="D2">
-        <v>166.0890355854674</v>
+        <v>166.6921228732276</v>
       </c>
       <c r="E2">
-        <v>-6.119999999999999</v>
+        <v>-4.1778</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.9422</v>
       </c>
       <c r="G2">
         <v>26.8</v>
@@ -1457,28 +1457,28 @@
         <v>12.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.09769265999999999</v>
       </c>
       <c r="N2">
-        <v>12.1</v>
+        <v>12.00230734</v>
       </c>
       <c r="O2">
-        <v>2.904</v>
+        <v>2.8805537616</v>
       </c>
       <c r="P2">
-        <v>9.196000000000002</v>
+        <v>9.121753578400002</v>
       </c>
       <c r="Q2">
-        <v>18.196</v>
+        <v>18.1217535784</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1079689613831751</v>
+        <v>0.1084462180564197</v>
       </c>
       <c r="T2">
-        <v>1.278259280003682</v>
+        <v>1.288072179526943</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>123.857821048173</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1077440358758555</v>
+        <v>0.1075191103685358</v>
       </c>
       <c r="C3">
-        <v>191.5499228732276</v>
+        <v>190.2152058728945</v>
       </c>
       <c r="D3">
-        <v>166.6921228732276</v>
+        <v>167.2996058728945</v>
       </c>
       <c r="E3">
-        <v>-4.1778</v>
+        <v>-2.235599999999999</v>
       </c>
       <c r="F3">
-        <v>1.9422</v>
+        <v>3.8844</v>
       </c>
       <c r="G3">
         <v>26.8</v>
@@ -1539,28 +1539,28 @@
         <v>12.1</v>
       </c>
       <c r="M3">
-        <v>0.09769265999999999</v>
+        <v>0.19538532</v>
       </c>
       <c r="N3">
-        <v>12.00230734</v>
+        <v>11.90461468</v>
       </c>
       <c r="O3">
-        <v>2.8805537616</v>
+        <v>2.8571075232</v>
       </c>
       <c r="P3">
-        <v>9.121753578400002</v>
+        <v>9.047507156800002</v>
       </c>
       <c r="Q3">
-        <v>18.1217535784</v>
+        <v>18.0475071568</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1084462180564197</v>
+        <v>0.1089332146617713</v>
       </c>
       <c r="T3">
-        <v>1.288072179526943</v>
+        <v>1.29808534230578</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>123.857821048173</v>
+        <v>61.92891052408648</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1075191103685358</v>
+        <v>0.1072941848612163</v>
       </c>
       <c r="C4">
-        <v>190.2152058728945</v>
+        <v>188.884932818674</v>
       </c>
       <c r="D4">
-        <v>167.2996058728945</v>
+        <v>167.911532818674</v>
       </c>
       <c r="E4">
-        <v>-2.235599999999999</v>
+        <v>-0.2933999999999992</v>
       </c>
       <c r="F4">
-        <v>3.8844</v>
+        <v>5.8266</v>
       </c>
       <c r="G4">
         <v>26.8</v>
@@ -1621,28 +1621,28 @@
         <v>12.1</v>
       </c>
       <c r="M4">
-        <v>0.19538532</v>
+        <v>0.29307798</v>
       </c>
       <c r="N4">
-        <v>11.90461468</v>
+        <v>11.80692202</v>
       </c>
       <c r="O4">
-        <v>2.8571075232</v>
+        <v>2.8336612848</v>
       </c>
       <c r="P4">
-        <v>9.047507156800002</v>
+        <v>8.973260735200002</v>
       </c>
       <c r="Q4">
-        <v>18.0475071568</v>
+        <v>17.9732607352</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1089332146617713</v>
+        <v>0.1094302524342436</v>
       </c>
       <c r="T4">
-        <v>1.29808534230578</v>
+        <v>1.308304962049129</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>61.92891052408648</v>
+        <v>41.28594034939098</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1072941848612163</v>
+        <v>0.1070692593538966</v>
       </c>
       <c r="C5">
-        <v>188.884932818674</v>
+        <v>187.5591526530629</v>
       </c>
       <c r="D5">
-        <v>167.911532818674</v>
+        <v>168.5279526530629</v>
       </c>
       <c r="E5">
-        <v>-0.2933999999999992</v>
+        <v>1.6488</v>
       </c>
       <c r="F5">
-        <v>5.8266</v>
+        <v>7.7688</v>
       </c>
       <c r="G5">
         <v>26.8</v>
@@ -1703,28 +1703,28 @@
         <v>12.1</v>
       </c>
       <c r="M5">
-        <v>0.29307798</v>
+        <v>0.3907706399999999</v>
       </c>
       <c r="N5">
-        <v>11.80692202</v>
+        <v>11.70922936</v>
       </c>
       <c r="O5">
-        <v>2.8336612848</v>
+        <v>2.8102150464</v>
       </c>
       <c r="P5">
-        <v>8.973260735200002</v>
+        <v>8.899014313600002</v>
       </c>
       <c r="Q5">
-        <v>17.9732607352</v>
+        <v>17.8990143136</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1094302524342436</v>
+        <v>0.109937645160309</v>
       </c>
       <c r="T5">
-        <v>1.308304962049129</v>
+        <v>1.318737490537132</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>41.28594034939098</v>
+        <v>30.96445526204324</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1070692593538966</v>
+        <v>0.106844333846577</v>
       </c>
       <c r="C6">
-        <v>187.5591526530629</v>
+        <v>186.2379150398963</v>
       </c>
       <c r="D6">
-        <v>168.5279526530629</v>
+        <v>169.1489150398963</v>
       </c>
       <c r="E6">
-        <v>1.6488</v>
+        <v>3.591000000000001</v>
       </c>
       <c r="F6">
-        <v>7.7688</v>
+        <v>9.711</v>
       </c>
       <c r="G6">
         <v>26.8</v>
@@ -1785,28 +1785,28 @@
         <v>12.1</v>
       </c>
       <c r="M6">
-        <v>0.3907706399999999</v>
+        <v>0.4884633</v>
       </c>
       <c r="N6">
-        <v>11.70922936</v>
+        <v>11.6115367</v>
       </c>
       <c r="O6">
-        <v>2.8102150464</v>
+        <v>2.786768808000001</v>
       </c>
       <c r="P6">
-        <v>8.899014313600002</v>
+        <v>8.824767892000001</v>
       </c>
       <c r="Q6">
-        <v>17.8990143136</v>
+        <v>17.824767892</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.109937645160309</v>
+        <v>0.1104557198385021</v>
       </c>
       <c r="T6">
-        <v>1.318737490537132</v>
+        <v>1.329389651203829</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.96445526204324</v>
+        <v>24.77156420963459</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.106844333846577</v>
+        <v>0.1066194083392574</v>
       </c>
       <c r="C7">
-        <v>186.2379150398963</v>
+        <v>184.9212703776873</v>
       </c>
       <c r="D7">
-        <v>169.1489150398963</v>
+        <v>169.7744703776873</v>
       </c>
       <c r="E7">
-        <v>3.591000000000001</v>
+        <v>5.533200000000001</v>
       </c>
       <c r="F7">
-        <v>9.711</v>
+        <v>11.6532</v>
       </c>
       <c r="G7">
         <v>26.8</v>
@@ -1867,28 +1867,28 @@
         <v>12.1</v>
       </c>
       <c r="M7">
-        <v>0.4884633</v>
+        <v>0.5861559599999999</v>
       </c>
       <c r="N7">
-        <v>11.6115367</v>
+        <v>11.51384404</v>
       </c>
       <c r="O7">
-        <v>2.786768808000001</v>
+        <v>2.763322569600001</v>
       </c>
       <c r="P7">
-        <v>8.824767892000001</v>
+        <v>8.750521470400002</v>
       </c>
       <c r="Q7">
-        <v>17.824767892</v>
+        <v>17.7505214704</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1104557198385021</v>
+        <v>0.1109848173821887</v>
       </c>
       <c r="T7">
-        <v>1.329389651203829</v>
+        <v>1.340268453586839</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.77156420963459</v>
+        <v>20.64297017469549</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1066194083392574</v>
+        <v>0.1063944828319378</v>
       </c>
       <c r="C8">
-        <v>184.9212703776873</v>
+        <v>183.6092698132619</v>
       </c>
       <c r="D8">
-        <v>169.7744703776873</v>
+        <v>170.4046698132619</v>
       </c>
       <c r="E8">
-        <v>5.533200000000001</v>
+        <v>7.475399999999999</v>
       </c>
       <c r="F8">
-        <v>11.6532</v>
+        <v>13.5954</v>
       </c>
       <c r="G8">
         <v>26.8</v>
@@ -1949,28 +1949,28 @@
         <v>12.1</v>
       </c>
       <c r="M8">
-        <v>0.5861559599999999</v>
+        <v>0.6838486199999999</v>
       </c>
       <c r="N8">
-        <v>11.51384404</v>
+        <v>11.41615138</v>
       </c>
       <c r="O8">
-        <v>2.763322569600001</v>
+        <v>2.739876331200001</v>
       </c>
       <c r="P8">
-        <v>8.750521470400002</v>
+        <v>8.676275048800001</v>
       </c>
       <c r="Q8">
-        <v>17.7505214704</v>
+        <v>17.6762750488</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1109848173821887</v>
+        <v>0.111525293367675</v>
       </c>
       <c r="T8">
-        <v>1.340268453586839</v>
+        <v>1.351381208709269</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.64297017469549</v>
+        <v>17.69397443545328</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1063944828319378</v>
+        <v>0.1061695573246181</v>
       </c>
       <c r="C9">
-        <v>183.6092698132619</v>
+        <v>182.3019652556995</v>
       </c>
       <c r="D9">
-        <v>170.4046698132619</v>
+        <v>171.0395652556995</v>
       </c>
       <c r="E9">
-        <v>7.475400000000002</v>
+        <v>9.4176</v>
       </c>
       <c r="F9">
-        <v>13.5954</v>
+        <v>15.5376</v>
       </c>
       <c r="G9">
         <v>26.8</v>
@@ -2031,28 +2031,28 @@
         <v>12.1</v>
       </c>
       <c r="M9">
-        <v>0.68384862</v>
+        <v>0.7815412799999999</v>
       </c>
       <c r="N9">
-        <v>11.41615138</v>
+        <v>11.31845872</v>
       </c>
       <c r="O9">
-        <v>2.739876331200001</v>
+        <v>2.7164300928</v>
       </c>
       <c r="P9">
-        <v>8.676275048800001</v>
+        <v>8.602028627200003</v>
       </c>
       <c r="Q9">
-        <v>17.6762750488</v>
+        <v>17.6020286272</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.111525293367675</v>
+        <v>0.1120775188311067</v>
       </c>
       <c r="T9">
-        <v>1.351381208709269</v>
+        <v>1.362735545464794</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.69397443545328</v>
+        <v>15.48222763102162</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1061695573246181</v>
+        <v>0.1059446318172985</v>
       </c>
       <c r="C10">
-        <v>182.3019652556995</v>
+        <v>180.9994093905864</v>
       </c>
       <c r="D10">
-        <v>171.0395652556995</v>
+        <v>171.6792093905864</v>
       </c>
       <c r="E10">
-        <v>9.4176</v>
+        <v>11.3598</v>
       </c>
       <c r="F10">
-        <v>15.5376</v>
+        <v>17.4798</v>
       </c>
       <c r="G10">
         <v>26.8</v>
@@ -2113,28 +2113,28 @@
         <v>12.1</v>
       </c>
       <c r="M10">
-        <v>0.7815412799999999</v>
+        <v>0.87923394</v>
       </c>
       <c r="N10">
-        <v>11.31845872</v>
+        <v>11.22076606</v>
       </c>
       <c r="O10">
-        <v>2.7164300928</v>
+        <v>2.6929838544</v>
       </c>
       <c r="P10">
-        <v>8.602028627200003</v>
+        <v>8.527782205600001</v>
       </c>
       <c r="Q10">
-        <v>17.6020286272</v>
+        <v>17.5277822056</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1120775188311067</v>
+        <v>0.1126418811179105</v>
       </c>
       <c r="T10">
-        <v>1.362735545464794</v>
+        <v>1.374339428083079</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.48222763102162</v>
+        <v>13.76198011646366</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1059446318172985</v>
+        <v>0.1058337063099789</v>
       </c>
       <c r="C11">
-        <v>180.9994093905864</v>
+        <v>179.3744245779938</v>
       </c>
       <c r="D11">
-        <v>171.6792093905864</v>
+        <v>171.9964245779938</v>
       </c>
       <c r="E11">
-        <v>11.3598</v>
+        <v>13.302</v>
       </c>
       <c r="F11">
-        <v>17.4798</v>
+        <v>19.422</v>
       </c>
       <c r="G11">
         <v>26.8</v>
@@ -2195,45 +2195,45 @@
         <v>12.1</v>
       </c>
       <c r="M11">
-        <v>0.87923394</v>
+        <v>1.0060596</v>
       </c>
       <c r="N11">
-        <v>11.22076606</v>
+        <v>11.0939404</v>
       </c>
       <c r="O11">
-        <v>2.6929838544</v>
+        <v>2.662545696</v>
       </c>
       <c r="P11">
-        <v>8.527782205600001</v>
+        <v>8.431394704000001</v>
       </c>
       <c r="Q11">
-        <v>17.5277822056</v>
+        <v>17.431394704</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1126418811179105</v>
+        <v>0.1132187847888655</v>
       </c>
       <c r="T11">
-        <v>1.374339428083079</v>
+        <v>1.386201174759548</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.24</v>
       </c>
       <c r="W11">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.76198011646366</v>
+        <v>12.02712046085541</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1058337063099789</v>
+        <v>0.1056201808026593</v>
       </c>
       <c r="C12">
-        <v>179.3744245779938</v>
+        <v>178.0461582592766</v>
       </c>
       <c r="D12">
-        <v>171.9964245779938</v>
+        <v>172.6103582592766</v>
       </c>
       <c r="E12">
-        <v>13.302</v>
+        <v>15.2442</v>
       </c>
       <c r="F12">
-        <v>19.422</v>
+        <v>21.3642</v>
       </c>
       <c r="G12">
         <v>26.8</v>
@@ -2277,28 +2277,28 @@
         <v>12.1</v>
       </c>
       <c r="M12">
-        <v>1.0060596</v>
+        <v>1.10666556</v>
       </c>
       <c r="N12">
-        <v>11.0939404</v>
+        <v>10.99333444</v>
       </c>
       <c r="O12">
-        <v>2.662545696</v>
+        <v>2.638400265600001</v>
       </c>
       <c r="P12">
-        <v>8.431394704000001</v>
+        <v>8.3549341744</v>
       </c>
       <c r="Q12">
-        <v>17.431394704</v>
+        <v>17.3549341744</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1132187847888655</v>
+        <v>0.1138086525872576</v>
       </c>
       <c r="T12">
-        <v>1.386201174759548</v>
+        <v>1.398329477541106</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.0271204608554</v>
+        <v>10.93374587350491</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1056201808026593</v>
+        <v>0.1054066552953397</v>
       </c>
       <c r="C13">
-        <v>178.0461582592766</v>
+        <v>176.7222904594868</v>
       </c>
       <c r="D13">
-        <v>172.6103582592766</v>
+        <v>173.2286904594868</v>
       </c>
       <c r="E13">
-        <v>15.2442</v>
+        <v>17.1864</v>
       </c>
       <c r="F13">
-        <v>21.3642</v>
+        <v>23.3064</v>
       </c>
       <c r="G13">
         <v>26.8</v>
@@ -2359,28 +2359,28 @@
         <v>12.1</v>
       </c>
       <c r="M13">
-        <v>1.10666556</v>
+        <v>1.20727152</v>
       </c>
       <c r="N13">
-        <v>10.99333444</v>
+        <v>10.89272848</v>
       </c>
       <c r="O13">
-        <v>2.638400265600001</v>
+        <v>2.614254835200001</v>
       </c>
       <c r="P13">
-        <v>8.3549341744</v>
+        <v>8.278473644800002</v>
       </c>
       <c r="Q13">
-        <v>17.3549341744</v>
+        <v>17.2784736448</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1138086525872576</v>
+        <v>0.1144119264719769</v>
       </c>
       <c r="T13">
-        <v>1.398329477541106</v>
+        <v>1.4107334235677</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.93374587350491</v>
+        <v>10.02260038404617</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1054066552953397</v>
+        <v>0.10536108978802</v>
       </c>
       <c r="C14">
-        <v>176.7222904594868</v>
+        <v>174.912614111945</v>
       </c>
       <c r="D14">
-        <v>173.2286904594868</v>
+        <v>173.361214111945</v>
       </c>
       <c r="E14">
-        <v>17.1864</v>
+        <v>19.1286</v>
       </c>
       <c r="F14">
-        <v>23.3064</v>
+        <v>25.2486</v>
       </c>
       <c r="G14">
         <v>26.8</v>
@@ -2441,45 +2441,45 @@
         <v>12.1</v>
       </c>
       <c r="M14">
-        <v>1.20727152</v>
+        <v>1.3508001</v>
       </c>
       <c r="N14">
-        <v>10.89272848</v>
+        <v>10.7491999</v>
       </c>
       <c r="O14">
-        <v>2.614254835200001</v>
+        <v>2.579807976</v>
       </c>
       <c r="P14">
-        <v>8.278473644800002</v>
+        <v>8.169391924000001</v>
       </c>
       <c r="Q14">
-        <v>17.2784736448</v>
+        <v>17.169391924</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1144119264719769</v>
+        <v>0.1150290687218621</v>
       </c>
       <c r="T14">
-        <v>1.4107334235677</v>
+        <v>1.423422517778813</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.24</v>
       </c>
       <c r="W14">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.02260038404617</v>
+        <v>8.957654059990077</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.10536108978802</v>
+        <v>0.1051604842807004</v>
       </c>
       <c r="C15">
-        <v>174.912614111945</v>
+        <v>173.5562788454943</v>
       </c>
       <c r="D15">
-        <v>173.361214111945</v>
+        <v>173.9470788454943</v>
       </c>
       <c r="E15">
-        <v>19.1286</v>
+        <v>21.07080000000001</v>
       </c>
       <c r="F15">
-        <v>25.2486</v>
+        <v>27.1908</v>
       </c>
       <c r="G15">
         <v>26.8</v>
@@ -2523,28 +2523,28 @@
         <v>12.1</v>
       </c>
       <c r="M15">
-        <v>1.3508001</v>
+        <v>1.4547078</v>
       </c>
       <c r="N15">
-        <v>10.7491999</v>
+        <v>10.6452922</v>
       </c>
       <c r="O15">
-        <v>2.579807976</v>
+        <v>2.554870128000001</v>
       </c>
       <c r="P15">
-        <v>8.169391924000001</v>
+        <v>8.090422072000001</v>
       </c>
       <c r="Q15">
-        <v>17.169391924</v>
+        <v>17.090422072</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1150290687218621</v>
+        <v>0.1156605631170935</v>
       </c>
       <c r="T15">
-        <v>1.423422517778813</v>
+        <v>1.436406707204137</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.957654059990077</v>
+        <v>8.317821627133641</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1051604842807004</v>
+        <v>0.1049598787733808</v>
       </c>
       <c r="C16">
-        <v>173.5562788454943</v>
+        <v>172.2039168019281</v>
       </c>
       <c r="D16">
-        <v>173.9470788454943</v>
+        <v>174.5369168019281</v>
       </c>
       <c r="E16">
-        <v>21.07080000000001</v>
+        <v>23.01300000000001</v>
       </c>
       <c r="F16">
-        <v>27.1908</v>
+        <v>29.133</v>
       </c>
       <c r="G16">
         <v>26.8</v>
@@ -2605,28 +2605,28 @@
         <v>12.1</v>
       </c>
       <c r="M16">
-        <v>1.4547078</v>
+        <v>1.5586155</v>
       </c>
       <c r="N16">
-        <v>10.6452922</v>
+        <v>10.5413845</v>
       </c>
       <c r="O16">
-        <v>2.554870128000001</v>
+        <v>2.52993228</v>
       </c>
       <c r="P16">
-        <v>8.090422072000001</v>
+        <v>8.011452220000001</v>
       </c>
       <c r="Q16">
-        <v>17.090422072</v>
+        <v>17.01145222</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1156605631170935</v>
+        <v>0.1163069162039774</v>
       </c>
       <c r="T16">
-        <v>1.436406707204137</v>
+        <v>1.449696406968882</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.317821627133641</v>
+        <v>7.763300185324733</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1049598787733808</v>
+        <v>0.1048565532660612</v>
       </c>
       <c r="C17">
-        <v>172.2039168019282</v>
+        <v>170.5670870695311</v>
       </c>
       <c r="D17">
-        <v>174.5369168019282</v>
+        <v>174.842287069531</v>
       </c>
       <c r="E17">
-        <v>23.013</v>
+        <v>24.9552</v>
       </c>
       <c r="F17">
-        <v>29.133</v>
+        <v>31.0752</v>
       </c>
       <c r="G17">
         <v>26.8</v>
@@ -2687,45 +2687,45 @@
         <v>12.1</v>
       </c>
       <c r="M17">
-        <v>1.5586155</v>
+        <v>1.68738336</v>
       </c>
       <c r="N17">
-        <v>10.5413845</v>
+        <v>10.41261664</v>
       </c>
       <c r="O17">
-        <v>2.52993228</v>
+        <v>2.4990279936</v>
       </c>
       <c r="P17">
-        <v>8.011452220000001</v>
+        <v>7.913588646400001</v>
       </c>
       <c r="Q17">
-        <v>17.01145222</v>
+        <v>16.9135886464</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1163069162039774</v>
+        <v>0.1169686586500728</v>
       </c>
       <c r="T17">
-        <v>1.449696406968881</v>
+        <v>1.463302528156596</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.24</v>
       </c>
       <c r="W17">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.763300185324733</v>
+        <v>7.170866020629718</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1048565532660612</v>
+        <v>0.1046620277587415</v>
       </c>
       <c r="C18">
-        <v>170.5670870695311</v>
+        <v>169.2027007448011</v>
       </c>
       <c r="D18">
-        <v>174.842287069531</v>
+        <v>175.4201007448011</v>
       </c>
       <c r="E18">
-        <v>24.9552</v>
+        <v>26.8974</v>
       </c>
       <c r="F18">
-        <v>31.0752</v>
+        <v>33.0174</v>
       </c>
       <c r="G18">
         <v>26.8</v>
@@ -2769,28 +2769,28 @@
         <v>12.1</v>
       </c>
       <c r="M18">
-        <v>1.68738336</v>
+        <v>1.79284482</v>
       </c>
       <c r="N18">
-        <v>10.41261664</v>
+        <v>10.30715518</v>
       </c>
       <c r="O18">
-        <v>2.4990279936</v>
+        <v>2.4737172432</v>
       </c>
       <c r="P18">
-        <v>7.913588646400001</v>
+        <v>7.833437936800001</v>
       </c>
       <c r="Q18">
-        <v>16.9135886464</v>
+        <v>16.8334379368</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1169686586500728</v>
+        <v>0.117646346697279</v>
       </c>
       <c r="T18">
-        <v>1.463302528156596</v>
+        <v>1.477236507686183</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.170866020629718</v>
+        <v>6.74905037235738</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1046620277587415</v>
+        <v>0.1044675022514219</v>
       </c>
       <c r="C19">
-        <v>169.2027007448011</v>
+        <v>167.8421461665748</v>
       </c>
       <c r="D19">
-        <v>175.4201007448011</v>
+        <v>176.0017461665748</v>
       </c>
       <c r="E19">
-        <v>26.8974</v>
+        <v>28.8396</v>
       </c>
       <c r="F19">
-        <v>33.0174</v>
+        <v>34.9596</v>
       </c>
       <c r="G19">
         <v>26.8</v>
@@ -2851,28 +2851,28 @@
         <v>12.1</v>
       </c>
       <c r="M19">
-        <v>1.79284482</v>
+        <v>1.89830628</v>
       </c>
       <c r="N19">
-        <v>10.30715518</v>
+        <v>10.20169372</v>
       </c>
       <c r="O19">
-        <v>2.4737172432</v>
+        <v>2.4484064928</v>
       </c>
       <c r="P19">
-        <v>7.833437936800001</v>
+        <v>7.753287227200001</v>
       </c>
       <c r="Q19">
-        <v>16.8334379368</v>
+        <v>16.7532872272</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.117646346697279</v>
+        <v>0.1183405637212463</v>
       </c>
       <c r="T19">
-        <v>1.477236507686183</v>
+        <v>1.491510340375028</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.74905037235738</v>
+        <v>6.374103129448637</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1044675022514219</v>
+        <v>0.1044173767441023</v>
       </c>
       <c r="C20">
-        <v>167.8421461665748</v>
+        <v>166.050450629684</v>
       </c>
       <c r="D20">
-        <v>176.0017461665748</v>
+        <v>176.1522506296839</v>
       </c>
       <c r="E20">
-        <v>28.8396</v>
+        <v>30.7818</v>
       </c>
       <c r="F20">
-        <v>34.9596</v>
+        <v>36.9018</v>
       </c>
       <c r="G20">
         <v>26.8</v>
@@ -2933,45 +2933,45 @@
         <v>12.1</v>
       </c>
       <c r="M20">
-        <v>1.89830628</v>
+        <v>2.04066954</v>
       </c>
       <c r="N20">
-        <v>10.20169372</v>
+        <v>10.05933046</v>
       </c>
       <c r="O20">
-        <v>2.4484064928</v>
+        <v>2.4142393104</v>
       </c>
       <c r="P20">
-        <v>7.753287227200001</v>
+        <v>7.645091149600002</v>
       </c>
       <c r="Q20">
-        <v>16.7532872272</v>
+        <v>16.6450911496</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1183405637212463</v>
+        <v>0.1190519219062992</v>
       </c>
       <c r="T20">
-        <v>1.491510340375028</v>
+        <v>1.506136613377178</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.374103129448637</v>
+        <v>5.929426476371084</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1044173767441023</v>
+        <v>0.1042304512367827</v>
       </c>
       <c r="C21">
-        <v>166.050450629684</v>
+        <v>164.6717812565657</v>
       </c>
       <c r="D21">
-        <v>176.1522506296839</v>
+        <v>176.7157812565657</v>
       </c>
       <c r="E21">
-        <v>30.7818</v>
+        <v>32.724</v>
       </c>
       <c r="F21">
-        <v>36.9018</v>
+        <v>38.844</v>
       </c>
       <c r="G21">
         <v>26.8</v>
@@ -3015,28 +3015,28 @@
         <v>12.1</v>
       </c>
       <c r="M21">
-        <v>2.04066954</v>
+        <v>2.1480732</v>
       </c>
       <c r="N21">
-        <v>10.05933046</v>
+        <v>9.951926800000001</v>
       </c>
       <c r="O21">
-        <v>2.4142393104</v>
+        <v>2.388462432</v>
       </c>
       <c r="P21">
-        <v>7.645091149600002</v>
+        <v>7.563464368</v>
       </c>
       <c r="Q21">
-        <v>16.6450911496</v>
+        <v>16.563464368</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1190519219062992</v>
+        <v>0.1197810640459784</v>
       </c>
       <c r="T21">
-        <v>1.506136613377178</v>
+        <v>1.521128543204381</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.929426476371084</v>
+        <v>5.63295515255253</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1042304512367827</v>
+        <v>0.1040435257294631</v>
       </c>
       <c r="C22">
-        <v>164.6717812565657</v>
+        <v>163.2967290493728</v>
       </c>
       <c r="D22">
-        <v>176.7157812565657</v>
+        <v>177.2829290493728</v>
       </c>
       <c r="E22">
-        <v>32.724</v>
+        <v>34.6662</v>
       </c>
       <c r="F22">
-        <v>38.844</v>
+        <v>40.7862</v>
       </c>
       <c r="G22">
         <v>26.8</v>
@@ -3097,28 +3097,28 @@
         <v>12.1</v>
       </c>
       <c r="M22">
-        <v>2.1480732</v>
+        <v>2.25547686</v>
       </c>
       <c r="N22">
-        <v>9.951926800000001</v>
+        <v>9.844523140000002</v>
       </c>
       <c r="O22">
-        <v>2.388462432</v>
+        <v>2.3626855536</v>
       </c>
       <c r="P22">
-        <v>7.563464368</v>
+        <v>7.481837586400001</v>
       </c>
       <c r="Q22">
-        <v>16.563464368</v>
+        <v>16.4818375864</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1197810640459784</v>
+        <v>0.120528665480333</v>
       </c>
       <c r="T22">
-        <v>1.521128543204381</v>
+        <v>1.536500015558856</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.63295515255253</v>
+        <v>5.364719192907172</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1040435257294631</v>
+        <v>0.1038566002221435</v>
       </c>
       <c r="C23">
-        <v>163.2967290493728</v>
+        <v>161.9253289467981</v>
       </c>
       <c r="D23">
-        <v>177.2829290493728</v>
+        <v>177.8537289467981</v>
       </c>
       <c r="E23">
-        <v>34.6662</v>
+        <v>36.6084</v>
       </c>
       <c r="F23">
-        <v>40.7862</v>
+        <v>42.7284</v>
       </c>
       <c r="G23">
         <v>26.8</v>
@@ -3179,28 +3179,28 @@
         <v>12.1</v>
       </c>
       <c r="M23">
-        <v>2.25547686</v>
+        <v>2.36288052</v>
       </c>
       <c r="N23">
-        <v>9.844523140000002</v>
+        <v>9.73711948</v>
       </c>
       <c r="O23">
-        <v>2.3626855536</v>
+        <v>2.3369086752</v>
       </c>
       <c r="P23">
-        <v>7.481837586400001</v>
+        <v>7.4002108048</v>
       </c>
       <c r="Q23">
-        <v>16.4818375864</v>
+        <v>16.4002108048</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.120528665480333</v>
+        <v>0.1212954361822352</v>
       </c>
       <c r="T23">
-        <v>1.536500015558856</v>
+        <v>1.552265628230112</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.364719192907172</v>
+        <v>5.1208683205023</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1038566002221435</v>
+        <v>0.1036696747148238</v>
       </c>
       <c r="C24">
-        <v>161.9253289467981</v>
+        <v>160.557616338958</v>
       </c>
       <c r="D24">
-        <v>177.8537289467981</v>
+        <v>178.428216338958</v>
       </c>
       <c r="E24">
-        <v>36.6084</v>
+        <v>38.5506</v>
       </c>
       <c r="F24">
-        <v>42.7284</v>
+        <v>44.6706</v>
       </c>
       <c r="G24">
         <v>26.8</v>
@@ -3261,28 +3261,28 @@
         <v>12.1</v>
       </c>
       <c r="M24">
-        <v>2.36288052</v>
+        <v>2.47028418</v>
       </c>
       <c r="N24">
-        <v>9.73711948</v>
+        <v>9.629715820000001</v>
       </c>
       <c r="O24">
-        <v>2.3369086752</v>
+        <v>2.3111317968</v>
       </c>
       <c r="P24">
-        <v>7.4002108048</v>
+        <v>7.318584023200001</v>
       </c>
       <c r="Q24">
-        <v>16.4002108048</v>
+        <v>16.3185840232</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1212954361822352</v>
+        <v>0.1220821230062647</v>
       </c>
       <c r="T24">
-        <v>1.552265628230112</v>
+        <v>1.568440737334388</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.1208683205023</v>
+        <v>4.898221871784808</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1036696747148238</v>
+        <v>0.1034827492075042</v>
       </c>
       <c r="C25">
-        <v>160.557616338958</v>
+        <v>159.1936270747071</v>
       </c>
       <c r="D25">
-        <v>178.428216338958</v>
+        <v>179.006427074707</v>
       </c>
       <c r="E25">
-        <v>38.5506</v>
+        <v>40.4928</v>
       </c>
       <c r="F25">
-        <v>44.6706</v>
+        <v>46.6128</v>
       </c>
       <c r="G25">
         <v>26.8</v>
@@ -3343,28 +3343,28 @@
         <v>12.1</v>
       </c>
       <c r="M25">
-        <v>2.47028418</v>
+        <v>2.57768784</v>
       </c>
       <c r="N25">
-        <v>9.629715820000001</v>
+        <v>9.522312160000002</v>
       </c>
       <c r="O25">
-        <v>2.3111317968</v>
+        <v>2.2853549184</v>
       </c>
       <c r="P25">
-        <v>7.318584023200001</v>
+        <v>7.236957241600002</v>
       </c>
       <c r="Q25">
-        <v>16.3185840232</v>
+        <v>16.2369572416</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1220821230062647</v>
+        <v>0.1228895121151371</v>
       </c>
       <c r="T25">
-        <v>1.568440737334388</v>
+        <v>1.585041507204565</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.898221871784808</v>
+        <v>4.694129293793775</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1034827492075042</v>
+        <v>0.1032958237001846</v>
       </c>
       <c r="C26">
-        <v>159.1936270747071</v>
+        <v>157.8333974690942</v>
       </c>
       <c r="D26">
-        <v>179.006427074707</v>
+        <v>179.5883974690942</v>
       </c>
       <c r="E26">
-        <v>40.4928</v>
+        <v>42.435</v>
       </c>
       <c r="F26">
-        <v>46.6128</v>
+        <v>48.555</v>
       </c>
       <c r="G26">
         <v>26.8</v>
@@ -3425,28 +3425,28 @@
         <v>12.1</v>
       </c>
       <c r="M26">
-        <v>2.57768784</v>
+        <v>2.6850915</v>
       </c>
       <c r="N26">
-        <v>9.522312160000002</v>
+        <v>9.414908500000001</v>
       </c>
       <c r="O26">
-        <v>2.2853549184</v>
+        <v>2.25957804</v>
       </c>
       <c r="P26">
-        <v>7.236957241600002</v>
+        <v>7.155330460000001</v>
       </c>
       <c r="Q26">
-        <v>16.2369572416</v>
+        <v>16.15533046</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1228895121151371</v>
+        <v>0.1237184316002461</v>
       </c>
       <c r="T26">
-        <v>1.585041507204565</v>
+        <v>1.602084964271281</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.694129293793775</v>
+        <v>4.506364122042024</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1032958237001846</v>
+        <v>0.103602898192865</v>
       </c>
       <c r="C27">
-        <v>157.8333974690942</v>
+        <v>154.9371446833654</v>
       </c>
       <c r="D27">
-        <v>179.5883974690942</v>
+        <v>178.6343446833654</v>
       </c>
       <c r="E27">
-        <v>42.435</v>
+        <v>44.3772</v>
       </c>
       <c r="F27">
-        <v>48.555</v>
+        <v>50.4972</v>
       </c>
       <c r="G27">
         <v>26.8</v>
@@ -3507,45 +3507,45 @@
         <v>12.1</v>
       </c>
       <c r="M27">
-        <v>2.6850915</v>
+        <v>2.91873816</v>
       </c>
       <c r="N27">
-        <v>9.414908500000001</v>
+        <v>9.181261840000001</v>
       </c>
       <c r="O27">
-        <v>2.25957804</v>
+        <v>2.2035028416</v>
       </c>
       <c r="P27">
-        <v>7.155330460000001</v>
+        <v>6.977758998400001</v>
       </c>
       <c r="Q27">
-        <v>16.15533046</v>
+        <v>15.9777589984</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1237184316002461</v>
+        <v>0.1245697543146824</v>
       </c>
       <c r="T27">
-        <v>1.602084964271281</v>
+        <v>1.619589055312773</v>
       </c>
       <c r="U27">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.24</v>
       </c>
       <c r="W27">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.506364122042024</v>
+        <v>4.145627095237622</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.103602898192865</v>
+        <v>0.1041531726855453</v>
       </c>
       <c r="C28">
-        <v>154.9371446833654</v>
+        <v>151.3104103406375</v>
       </c>
       <c r="D28">
-        <v>178.6343446833654</v>
+        <v>176.9498103406375</v>
       </c>
       <c r="E28">
-        <v>44.3772</v>
+        <v>46.31940000000001</v>
       </c>
       <c r="F28">
-        <v>50.4972</v>
+        <v>52.43940000000001</v>
       </c>
       <c r="G28">
         <v>26.8</v>
@@ -3589,45 +3589,45 @@
         <v>12.1</v>
       </c>
       <c r="M28">
-        <v>2.91873816</v>
+        <v>3.214535220000001</v>
       </c>
       <c r="N28">
-        <v>9.181261840000001</v>
+        <v>8.885464780000001</v>
       </c>
       <c r="O28">
-        <v>2.2035028416</v>
+        <v>2.1325115472</v>
       </c>
       <c r="P28">
-        <v>6.977758998400001</v>
+        <v>6.752953232800001</v>
       </c>
       <c r="Q28">
-        <v>15.9777589984</v>
+        <v>15.7529532328</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1245697543146824</v>
+        <v>0.1254444009391032</v>
       </c>
       <c r="T28">
-        <v>1.619589055312773</v>
+        <v>1.637572710492388</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.145627095237622</v>
+        <v>3.764152255889733</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1041531726855453</v>
+        <v>0.1040118471782257</v>
       </c>
       <c r="C29">
-        <v>151.3104103406375</v>
+        <v>149.7978053960897</v>
       </c>
       <c r="D29">
-        <v>176.9498103406375</v>
+        <v>177.3794053960897</v>
       </c>
       <c r="E29">
-        <v>46.31940000000001</v>
+        <v>48.26160000000001</v>
       </c>
       <c r="F29">
-        <v>52.43940000000001</v>
+        <v>54.38160000000001</v>
       </c>
       <c r="G29">
         <v>26.8</v>
@@ -3671,28 +3671,28 @@
         <v>12.1</v>
       </c>
       <c r="M29">
-        <v>3.214535220000001</v>
+        <v>3.33359208</v>
       </c>
       <c r="N29">
-        <v>8.885464780000001</v>
+        <v>8.766407920000001</v>
       </c>
       <c r="O29">
-        <v>2.1325115472</v>
+        <v>2.1039379008</v>
       </c>
       <c r="P29">
-        <v>6.752953232800001</v>
+        <v>6.662470019200001</v>
       </c>
       <c r="Q29">
-        <v>15.7529532328</v>
+        <v>15.6624700192</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1254444009391032</v>
+        <v>0.1263433433030913</v>
       </c>
       <c r="T29">
-        <v>1.637572710492388</v>
+        <v>1.656055911649214</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.764152255889733</v>
+        <v>3.629718246750814</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1040118471782257</v>
+        <v>0.1038705216709061</v>
       </c>
       <c r="C30">
-        <v>149.7978053960897</v>
+        <v>148.287291451843</v>
       </c>
       <c r="D30">
-        <v>177.3794053960897</v>
+        <v>177.811091451843</v>
       </c>
       <c r="E30">
-        <v>48.26160000000001</v>
+        <v>50.20380000000001</v>
       </c>
       <c r="F30">
-        <v>54.38160000000001</v>
+        <v>56.32380000000001</v>
       </c>
       <c r="G30">
         <v>26.8</v>
@@ -3753,28 +3753,28 @@
         <v>12.1</v>
       </c>
       <c r="M30">
-        <v>3.33359208</v>
+        <v>3.45264894</v>
       </c>
       <c r="N30">
-        <v>8.766407920000001</v>
+        <v>8.647351060000002</v>
       </c>
       <c r="O30">
-        <v>2.1039379008</v>
+        <v>2.0753642544</v>
       </c>
       <c r="P30">
-        <v>6.662470019200001</v>
+        <v>6.571986805600002</v>
       </c>
       <c r="Q30">
-        <v>15.6624700192</v>
+        <v>15.5719868056</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1263433433030913</v>
+        <v>0.1272676079871917</v>
       </c>
       <c r="T30">
-        <v>1.656055911649214</v>
+        <v>1.675059766359754</v>
       </c>
       <c r="U30">
         <v>0.0613</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.629718246750814</v>
+        <v>3.504555548586993</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1038705216709061</v>
+        <v>0.1043675961635865</v>
       </c>
       <c r="C31">
-        <v>148.287291451843</v>
+        <v>144.835974399651</v>
       </c>
       <c r="D31">
-        <v>177.811091451843</v>
+        <v>176.301974399651</v>
       </c>
       <c r="E31">
-        <v>50.2038</v>
+        <v>52.146</v>
       </c>
       <c r="F31">
-        <v>56.3238</v>
+        <v>58.266</v>
       </c>
       <c r="G31">
         <v>26.8</v>
@@ -3835,45 +3835,45 @@
         <v>12.1</v>
       </c>
       <c r="M31">
-        <v>3.45264894</v>
+        <v>3.7348506</v>
       </c>
       <c r="N31">
-        <v>8.647351060000002</v>
+        <v>8.365149400000002</v>
       </c>
       <c r="O31">
-        <v>2.0753642544</v>
+        <v>2.007635856</v>
       </c>
       <c r="P31">
-        <v>6.571986805600002</v>
+        <v>6.357513544000001</v>
       </c>
       <c r="Q31">
-        <v>15.5719868056</v>
+        <v>15.357513544</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1272676079871917</v>
+        <v>0.128218280233695</v>
       </c>
       <c r="T31">
-        <v>1.675059766359754</v>
+        <v>1.694606588347738</v>
       </c>
       <c r="U31">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0.24</v>
       </c>
       <c r="W31">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.504555548586993</v>
+        <v>3.239754757526312</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1043675961635865</v>
+        <v>0.1042475506562669</v>
       </c>
       <c r="C32">
-        <v>144.835974399651</v>
+        <v>143.2558812753133</v>
       </c>
       <c r="D32">
-        <v>176.301974399651</v>
+        <v>176.6640812753133</v>
       </c>
       <c r="E32">
-        <v>52.146</v>
+        <v>54.0882</v>
       </c>
       <c r="F32">
-        <v>58.266</v>
+        <v>60.2082</v>
       </c>
       <c r="G32">
         <v>26.8</v>
@@ -3917,28 +3917,28 @@
         <v>12.1</v>
       </c>
       <c r="M32">
-        <v>3.7348506</v>
+        <v>3.85934562</v>
       </c>
       <c r="N32">
-        <v>8.365149400000002</v>
+        <v>8.240654380000002</v>
       </c>
       <c r="O32">
-        <v>2.007635856</v>
+        <v>1.9777570512</v>
       </c>
       <c r="P32">
-        <v>6.357513544000001</v>
+        <v>6.262897328800002</v>
       </c>
       <c r="Q32">
-        <v>15.357513544</v>
+        <v>15.2628973288</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.128218280233695</v>
+        <v>0.1291965081974882</v>
       </c>
       <c r="T32">
-        <v>1.694606588347738</v>
+        <v>1.714719984886098</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.239754757526312</v>
+        <v>3.135246539541593</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1042475506562669</v>
+        <v>0.1041275051489473</v>
       </c>
       <c r="C33">
-        <v>143.2558812753133</v>
+        <v>141.6772786760197</v>
       </c>
       <c r="D33">
-        <v>176.6640812753133</v>
+        <v>177.0276786760197</v>
       </c>
       <c r="E33">
-        <v>54.0882</v>
+        <v>56.0304</v>
       </c>
       <c r="F33">
-        <v>60.2082</v>
+        <v>62.1504</v>
       </c>
       <c r="G33">
         <v>26.8</v>
@@ -3999,28 +3999,28 @@
         <v>12.1</v>
       </c>
       <c r="M33">
-        <v>3.85934562</v>
+        <v>3.98384064</v>
       </c>
       <c r="N33">
-        <v>8.240654380000002</v>
+        <v>8.116159360000001</v>
       </c>
       <c r="O33">
-        <v>1.9777570512</v>
+        <v>1.9478782464</v>
       </c>
       <c r="P33">
-        <v>6.262897328800002</v>
+        <v>6.168281113600001</v>
       </c>
       <c r="Q33">
-        <v>15.2628973288</v>
+        <v>15.1682811136</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1291965081974882</v>
+        <v>0.1302035075719813</v>
       </c>
       <c r="T33">
-        <v>1.714719984886098</v>
+        <v>1.735424951910881</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.135246539541593</v>
+        <v>3.037270085180918</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1041275051489473</v>
+        <v>0.1059636996416276</v>
       </c>
       <c r="C34">
-        <v>141.6772786760197</v>
+        <v>134.332198690694</v>
       </c>
       <c r="D34">
-        <v>177.0276786760197</v>
+        <v>171.624798690694</v>
       </c>
       <c r="E34">
-        <v>56.0304</v>
+        <v>57.97260000000001</v>
       </c>
       <c r="F34">
-        <v>62.1504</v>
+        <v>64.0926</v>
       </c>
       <c r="G34">
         <v>26.8</v>
@@ -4081,45 +4081,45 @@
         <v>12.1</v>
       </c>
       <c r="M34">
-        <v>3.98384064</v>
+        <v>4.608257940000001</v>
       </c>
       <c r="N34">
-        <v>8.116159360000001</v>
+        <v>7.491742060000001</v>
       </c>
       <c r="O34">
-        <v>1.9478782464</v>
+        <v>1.7980180944</v>
       </c>
       <c r="P34">
-        <v>6.168281113600001</v>
+        <v>5.6937239656</v>
       </c>
       <c r="Q34">
-        <v>15.1682811136</v>
+        <v>14.6937239656</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1302035075719813</v>
+        <v>0.131240566629295</v>
       </c>
       <c r="T34">
-        <v>1.735424951910881</v>
+        <v>1.756747977652821</v>
       </c>
       <c r="U34">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V34">
         <v>0.24</v>
       </c>
       <c r="W34">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.037270085180918</v>
+        <v>2.625721076715597</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1059636996416276</v>
+        <v>0.105902934134308</v>
       </c>
       <c r="C35">
-        <v>134.332198690694</v>
+        <v>132.5635154767091</v>
       </c>
       <c r="D35">
-        <v>171.624798690694</v>
+        <v>171.7983154767091</v>
       </c>
       <c r="E35">
-        <v>57.97260000000001</v>
+        <v>59.91480000000001</v>
       </c>
       <c r="F35">
-        <v>64.0926</v>
+        <v>66.0348</v>
       </c>
       <c r="G35">
         <v>26.8</v>
@@ -4163,28 +4163,28 @@
         <v>12.1</v>
       </c>
       <c r="M35">
-        <v>4.608257940000001</v>
+        <v>4.747902120000001</v>
       </c>
       <c r="N35">
-        <v>7.491742060000001</v>
+        <v>7.352097880000001</v>
       </c>
       <c r="O35">
-        <v>1.7980180944</v>
+        <v>1.7645034912</v>
       </c>
       <c r="P35">
-        <v>5.6937239656</v>
+        <v>5.5875943888</v>
       </c>
       <c r="Q35">
-        <v>14.6937239656</v>
+        <v>14.5875943888</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.131240566629295</v>
+        <v>0.1323090517186485</v>
       </c>
       <c r="T35">
-        <v>1.756747977652821</v>
+        <v>1.778717155689972</v>
       </c>
       <c r="U35">
         <v>0.07190000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.625721076715597</v>
+        <v>2.548493986223962</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.105902934134308</v>
+        <v>0.1068795686269884</v>
       </c>
       <c r="C36">
-        <v>132.5635154767091</v>
+        <v>127.8743386323966</v>
       </c>
       <c r="D36">
-        <v>171.7983154767091</v>
+        <v>169.0513386323966</v>
       </c>
       <c r="E36">
-        <v>59.91480000000001</v>
+        <v>61.85700000000001</v>
       </c>
       <c r="F36">
-        <v>66.0348</v>
+        <v>67.977</v>
       </c>
       <c r="G36">
         <v>26.8</v>
@@ -4245,45 +4245,45 @@
         <v>12.1</v>
       </c>
       <c r="M36">
-        <v>4.747902120000001</v>
+        <v>5.152656600000001</v>
       </c>
       <c r="N36">
-        <v>7.352097880000001</v>
+        <v>6.9473434</v>
       </c>
       <c r="O36">
-        <v>1.7645034912</v>
+        <v>1.667362416</v>
       </c>
       <c r="P36">
-        <v>5.5875943888</v>
+        <v>5.279980984</v>
       </c>
       <c r="Q36">
-        <v>14.5875943888</v>
+        <v>14.279980984</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1323090517186485</v>
+        <v>0.1334104132722898</v>
       </c>
       <c r="T36">
-        <v>1.778717155689972</v>
+        <v>1.801362308435958</v>
       </c>
       <c r="U36">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
         <v>0.24</v>
       </c>
       <c r="W36">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.548493986223962</v>
+        <v>2.348303203438785</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1068795686269884</v>
+        <v>0.1068484431196688</v>
       </c>
       <c r="C37">
-        <v>127.8743386323966</v>
+        <v>126.0183293427425</v>
       </c>
       <c r="D37">
-        <v>169.0513386323966</v>
+        <v>169.1375293427425</v>
       </c>
       <c r="E37">
-        <v>61.85700000000001</v>
+        <v>63.79920000000001</v>
       </c>
       <c r="F37">
-        <v>67.977</v>
+        <v>69.9192</v>
       </c>
       <c r="G37">
         <v>26.8</v>
@@ -4327,28 +4327,28 @@
         <v>12.1</v>
       </c>
       <c r="M37">
-        <v>5.152656600000001</v>
+        <v>5.299875360000001</v>
       </c>
       <c r="N37">
-        <v>6.9473434</v>
+        <v>6.800124640000001</v>
       </c>
       <c r="O37">
-        <v>1.667362416</v>
+        <v>1.6320299136</v>
       </c>
       <c r="P37">
-        <v>5.279980984</v>
+        <v>5.168094726400001</v>
       </c>
       <c r="Q37">
-        <v>14.279980984</v>
+        <v>14.1680947264</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1334104132722898</v>
+        <v>0.1345461923744825</v>
       </c>
       <c r="T37">
-        <v>1.801362308435958</v>
+        <v>1.824715122205256</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.348303203438785</v>
+        <v>2.283072558898819</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1068484431196688</v>
+        <v>0.1068173176123492</v>
       </c>
       <c r="C38">
-        <v>126.0183293427424</v>
+        <v>124.1624079864715</v>
       </c>
       <c r="D38">
-        <v>169.1375293427424</v>
+        <v>169.2238079864715</v>
       </c>
       <c r="E38">
-        <v>63.79920000000001</v>
+        <v>65.7414</v>
       </c>
       <c r="F38">
-        <v>69.9192</v>
+        <v>71.8614</v>
       </c>
       <c r="G38">
         <v>26.8</v>
@@ -4409,28 +4409,28 @@
         <v>12.1</v>
       </c>
       <c r="M38">
-        <v>5.299875360000001</v>
+        <v>5.447094120000001</v>
       </c>
       <c r="N38">
-        <v>6.800124640000001</v>
+        <v>6.65290588</v>
       </c>
       <c r="O38">
-        <v>1.6320299136</v>
+        <v>1.5966974112</v>
       </c>
       <c r="P38">
-        <v>5.168094726400001</v>
+        <v>5.0562084688</v>
       </c>
       <c r="Q38">
-        <v>14.1680947264</v>
+        <v>14.0562084688</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1345461923744825</v>
+        <v>0.1357180279561098</v>
       </c>
       <c r="T38">
-        <v>1.824715122205256</v>
+        <v>1.848809295141833</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.283072558898819</v>
+        <v>2.221367895144797</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1068173176123492</v>
+        <v>0.1067861921050295</v>
       </c>
       <c r="C39">
-        <v>124.1624079864715</v>
+        <v>122.3065746982194</v>
       </c>
       <c r="D39">
-        <v>169.2238079864715</v>
+        <v>169.3101746982194</v>
       </c>
       <c r="E39">
-        <v>65.7414</v>
+        <v>67.6836</v>
       </c>
       <c r="F39">
-        <v>71.8614</v>
+        <v>73.8036</v>
       </c>
       <c r="G39">
         <v>26.8</v>
@@ -4491,28 +4491,28 @@
         <v>12.1</v>
       </c>
       <c r="M39">
-        <v>5.447094120000001</v>
+        <v>5.59431288</v>
       </c>
       <c r="N39">
-        <v>6.65290588</v>
+        <v>6.505687120000001</v>
       </c>
       <c r="O39">
-        <v>1.5966974112</v>
+        <v>1.5613649088</v>
       </c>
       <c r="P39">
-        <v>5.0562084688</v>
+        <v>4.944322211200001</v>
       </c>
       <c r="Q39">
-        <v>14.0562084688</v>
+        <v>13.9443222112</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1357180279561098</v>
+        <v>0.1369276646855315</v>
       </c>
       <c r="T39">
-        <v>1.848809295141833</v>
+        <v>1.873680699463461</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.221367895144797</v>
+        <v>2.162910845272566</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1067861921050295</v>
+        <v>0.1067550665977099</v>
       </c>
       <c r="C40">
-        <v>122.3065746982194</v>
+        <v>120.4508296128967</v>
       </c>
       <c r="D40">
-        <v>169.3101746982194</v>
+        <v>169.3966296128967</v>
       </c>
       <c r="E40">
-        <v>67.6836</v>
+        <v>69.6258</v>
       </c>
       <c r="F40">
-        <v>73.8036</v>
+        <v>75.7458</v>
       </c>
       <c r="G40">
         <v>26.8</v>
@@ -4573,28 +4573,28 @@
         <v>12.1</v>
       </c>
       <c r="M40">
-        <v>5.59431288</v>
+        <v>5.741531640000001</v>
       </c>
       <c r="N40">
-        <v>6.505687120000001</v>
+        <v>6.358468360000001</v>
       </c>
       <c r="O40">
-        <v>1.5613649088</v>
+        <v>1.5260324064</v>
       </c>
       <c r="P40">
-        <v>4.944322211200001</v>
+        <v>4.832435953600001</v>
       </c>
       <c r="Q40">
-        <v>13.9443222112</v>
+        <v>13.8324359536</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1369276646855315</v>
+        <v>0.13817696163559</v>
       </c>
       <c r="T40">
-        <v>1.873680699463461</v>
+        <v>1.899367559664487</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.162910845272566</v>
+        <v>2.107451592829679</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1067550665977099</v>
+        <v>0.1067239410903903</v>
       </c>
       <c r="C41">
-        <v>120.4508296128967</v>
+        <v>118.5951728656898</v>
       </c>
       <c r="D41">
-        <v>169.3966296128967</v>
+        <v>169.4831728656898</v>
       </c>
       <c r="E41">
-        <v>69.6258</v>
+        <v>71.568</v>
       </c>
       <c r="F41">
-        <v>75.7458</v>
+        <v>77.688</v>
       </c>
       <c r="G41">
         <v>26.8</v>
@@ -4655,28 +4655,28 @@
         <v>12.1</v>
       </c>
       <c r="M41">
-        <v>5.741531640000001</v>
+        <v>5.888750400000001</v>
       </c>
       <c r="N41">
-        <v>6.358468360000001</v>
+        <v>6.2112496</v>
       </c>
       <c r="O41">
-        <v>1.5260324064</v>
+        <v>1.490699904</v>
       </c>
       <c r="P41">
-        <v>4.832435953600001</v>
+        <v>4.720549696000001</v>
       </c>
       <c r="Q41">
-        <v>13.8324359536</v>
+        <v>13.720549696</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.13817696163559</v>
+        <v>0.1394679018173172</v>
       </c>
       <c r="T41">
-        <v>1.899367559664487</v>
+        <v>1.925910648538881</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.107451592829679</v>
+        <v>2.054765303008937</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1067239410903903</v>
+        <v>0.1066928155830707</v>
       </c>
       <c r="C42">
-        <v>118.5951728656898</v>
+        <v>116.7396045920613</v>
       </c>
       <c r="D42">
-        <v>169.4831728656898</v>
+        <v>169.5698045920613</v>
       </c>
       <c r="E42">
-        <v>71.568</v>
+        <v>73.5102</v>
       </c>
       <c r="F42">
-        <v>77.688</v>
+        <v>79.6302</v>
       </c>
       <c r="G42">
         <v>26.8</v>
@@ -4737,28 +4737,28 @@
         <v>12.1</v>
       </c>
       <c r="M42">
-        <v>5.888750400000001</v>
+        <v>6.03596916</v>
       </c>
       <c r="N42">
-        <v>6.2112496</v>
+        <v>6.064030840000001</v>
       </c>
       <c r="O42">
-        <v>1.490699904</v>
+        <v>1.4553674016</v>
       </c>
       <c r="P42">
-        <v>4.720549696000001</v>
+        <v>4.608663438400001</v>
       </c>
       <c r="Q42">
-        <v>13.720549696</v>
+        <v>13.6086634384</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1394679018173172</v>
+        <v>0.1408026026831706</v>
       </c>
       <c r="T42">
-        <v>1.925910648538881</v>
+        <v>1.95335350313783</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.054765303008937</v>
+        <v>2.00464907610628</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1066928155830707</v>
+        <v>0.1111943300757511</v>
       </c>
       <c r="C43">
-        <v>116.7396045920613</v>
+        <v>103.1248187270798</v>
       </c>
       <c r="D43">
-        <v>169.5698045920613</v>
+        <v>157.8972187270798</v>
       </c>
       <c r="E43">
-        <v>73.5102</v>
+        <v>75.4524</v>
       </c>
       <c r="F43">
-        <v>79.6302</v>
+        <v>81.5724</v>
       </c>
       <c r="G43">
         <v>26.8</v>
@@ -4819,45 +4819,45 @@
         <v>12.1</v>
       </c>
       <c r="M43">
-        <v>6.03596916</v>
+        <v>7.341515999999999</v>
       </c>
       <c r="N43">
-        <v>6.064030840000001</v>
+        <v>4.758484000000002</v>
       </c>
       <c r="O43">
-        <v>1.4553674016</v>
+        <v>1.14203616</v>
       </c>
       <c r="P43">
-        <v>4.608663438400001</v>
+        <v>3.616447840000002</v>
       </c>
       <c r="Q43">
-        <v>13.6086634384</v>
+        <v>12.61644784</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1408026026831706</v>
+        <v>0.1421833277168122</v>
       </c>
       <c r="T43">
-        <v>1.95335350313783</v>
+        <v>1.981742663067777</v>
       </c>
       <c r="U43">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V43">
         <v>0.24</v>
       </c>
       <c r="W43">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.00464907610628</v>
+        <v>1.648160952043148</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1111943300757511</v>
+        <v>0.1112711245684314</v>
       </c>
       <c r="C44">
-        <v>103.1248187270798</v>
+        <v>100.9974128536857</v>
       </c>
       <c r="D44">
-        <v>157.8972187270798</v>
+        <v>157.7120128536857</v>
       </c>
       <c r="E44">
-        <v>75.4524</v>
+        <v>77.3946</v>
       </c>
       <c r="F44">
-        <v>81.5724</v>
+        <v>83.5146</v>
       </c>
       <c r="G44">
         <v>26.8</v>
@@ -4901,28 +4901,28 @@
         <v>12.1</v>
       </c>
       <c r="M44">
-        <v>7.341515999999999</v>
+        <v>7.516313999999999</v>
       </c>
       <c r="N44">
-        <v>4.758484000000002</v>
+        <v>4.583686000000002</v>
       </c>
       <c r="O44">
-        <v>1.14203616</v>
+        <v>1.10008464</v>
       </c>
       <c r="P44">
-        <v>3.616447840000002</v>
+        <v>3.483601360000002</v>
       </c>
       <c r="Q44">
-        <v>12.61644784</v>
+        <v>12.48360136</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1421833277168122</v>
+        <v>0.1436124992428622</v>
       </c>
       <c r="T44">
-        <v>1.981742663067777</v>
+        <v>2.011127933872459</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.648160952043148</v>
+        <v>1.609831627577028</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1112711245684314</v>
+        <v>0.1113479190611118</v>
       </c>
       <c r="C45">
-        <v>100.9974128536857</v>
+        <v>98.87044094650427</v>
       </c>
       <c r="D45">
-        <v>157.7120128536857</v>
+        <v>157.5272409465043</v>
       </c>
       <c r="E45">
-        <v>77.3946</v>
+        <v>79.3368</v>
       </c>
       <c r="F45">
-        <v>83.5146</v>
+        <v>85.4568</v>
       </c>
       <c r="G45">
         <v>26.8</v>
@@ -4983,28 +4983,28 @@
         <v>12.1</v>
       </c>
       <c r="M45">
-        <v>7.516313999999999</v>
+        <v>7.691112</v>
       </c>
       <c r="N45">
-        <v>4.583686000000002</v>
+        <v>4.408888000000002</v>
       </c>
       <c r="O45">
-        <v>1.10008464</v>
+        <v>1.05813312</v>
       </c>
       <c r="P45">
-        <v>3.483601360000002</v>
+        <v>3.350754880000002</v>
       </c>
       <c r="Q45">
-        <v>12.48360136</v>
+        <v>12.35075488</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1436124992428622</v>
+        <v>0.1450927126091282</v>
       </c>
       <c r="T45">
-        <v>2.011127933872459</v>
+        <v>2.041562678634452</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.609831627577028</v>
+        <v>1.573244545132096</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1113479190611118</v>
+        <v>0.1114247135537922</v>
       </c>
       <c r="C46">
-        <v>98.87044094650427</v>
+        <v>96.74390148204458</v>
       </c>
       <c r="D46">
-        <v>157.5272409465043</v>
+        <v>157.3429014820446</v>
       </c>
       <c r="E46">
-        <v>79.3368</v>
+        <v>81.279</v>
       </c>
       <c r="F46">
-        <v>85.4568</v>
+        <v>87.399</v>
       </c>
       <c r="G46">
         <v>26.8</v>
@@ -5065,28 +5065,28 @@
         <v>12.1</v>
       </c>
       <c r="M46">
-        <v>7.691112</v>
+        <v>7.86591</v>
       </c>
       <c r="N46">
-        <v>4.408888000000002</v>
+        <v>4.234090000000002</v>
       </c>
       <c r="O46">
-        <v>1.05813312</v>
+        <v>1.0161816</v>
       </c>
       <c r="P46">
-        <v>3.350754880000002</v>
+        <v>3.217908400000002</v>
       </c>
       <c r="Q46">
-        <v>12.35075488</v>
+        <v>12.2179084</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1450927126091282</v>
+        <v>0.1466267519159858</v>
       </c>
       <c r="T46">
-        <v>2.041562678634452</v>
+        <v>2.073104141387789</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.573244545132096</v>
+        <v>1.538283555240271</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1114247135537922</v>
+        <v>0.1115015080464726</v>
       </c>
       <c r="C47">
-        <v>96.74390148204458</v>
+        <v>94.6177929439388</v>
       </c>
       <c r="D47">
-        <v>157.3429014820446</v>
+        <v>157.1589929439388</v>
       </c>
       <c r="E47">
-        <v>81.279</v>
+        <v>83.2212</v>
       </c>
       <c r="F47">
-        <v>87.399</v>
+        <v>89.3412</v>
       </c>
       <c r="G47">
         <v>26.8</v>
@@ -5147,28 +5147,28 @@
         <v>12.1</v>
       </c>
       <c r="M47">
-        <v>7.86591</v>
+        <v>8.040708</v>
       </c>
       <c r="N47">
-        <v>4.234090000000002</v>
+        <v>4.059292000000001</v>
       </c>
       <c r="O47">
-        <v>1.0161816</v>
+        <v>0.9742300800000002</v>
       </c>
       <c r="P47">
-        <v>3.217908400000002</v>
+        <v>3.085061920000001</v>
       </c>
       <c r="Q47">
-        <v>12.2179084</v>
+        <v>12.08506192</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1466267519159858</v>
+        <v>0.1482176074934677</v>
       </c>
       <c r="T47">
-        <v>2.073104141387789</v>
+        <v>2.105813806465325</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.538283555240271</v>
+        <v>1.504842608387222</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1115015080464726</v>
+        <v>0.134154709449964</v>
       </c>
       <c r="C48">
-        <v>94.6177929439388</v>
+        <v>52.38171000671878</v>
       </c>
       <c r="D48">
-        <v>157.1589929439388</v>
+        <v>116.8651100067188</v>
       </c>
       <c r="E48">
-        <v>83.2212</v>
+        <v>85.1634</v>
       </c>
       <c r="F48">
-        <v>89.3412</v>
+        <v>91.2834</v>
       </c>
       <c r="G48">
         <v>26.8</v>
@@ -5229,45 +5229,45 @@
         <v>12.1</v>
       </c>
       <c r="M48">
-        <v>8.040708</v>
+        <v>13.40040312</v>
       </c>
       <c r="N48">
-        <v>4.059292000000001</v>
+        <v>-1.30040312</v>
       </c>
       <c r="O48">
-        <v>0.9742300800000002</v>
+        <v>-0.3120967488000001</v>
       </c>
       <c r="P48">
-        <v>3.085061920000001</v>
+        <v>-0.9883063712000002</v>
       </c>
       <c r="Q48">
-        <v>12.08506192</v>
+        <v>8.0116936288</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1482176074934677</v>
+        <v>0.1511525011450933</v>
       </c>
       <c r="T48">
-        <v>2.105813806465325</v>
+        <v>2.166158308971837</v>
       </c>
       <c r="U48">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.24</v>
+        <v>0.2167098985004266</v>
       </c>
       <c r="W48">
-        <v>0.0684</v>
+        <v>0.1149869869001374</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.504842608387222</v>
+        <v>0.9029579104184442</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.134154709449964</v>
+        <v>0.135164709449964</v>
       </c>
       <c r="C49">
-        <v>52.38171000671878</v>
+        <v>49.11870046307142</v>
       </c>
       <c r="D49">
-        <v>116.8651100067188</v>
+        <v>115.5443004630714</v>
       </c>
       <c r="E49">
-        <v>85.1634</v>
+        <v>87.1056</v>
       </c>
       <c r="F49">
-        <v>91.2834</v>
+        <v>93.2256</v>
       </c>
       <c r="G49">
         <v>26.8</v>
@@ -5311,37 +5311,37 @@
         <v>12.1</v>
       </c>
       <c r="M49">
-        <v>13.40040312</v>
+        <v>13.68551808</v>
       </c>
       <c r="N49">
-        <v>-1.30040312</v>
+        <v>-1.58551808</v>
       </c>
       <c r="O49">
-        <v>-0.3120967488000001</v>
+        <v>-0.3805243392</v>
       </c>
       <c r="P49">
-        <v>-0.9883063712000002</v>
+        <v>-1.2049937408</v>
       </c>
       <c r="Q49">
-        <v>8.0116936288</v>
+        <v>7.7950062592</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1511525011450933</v>
+        <v>0.1531785107824989</v>
       </c>
       <c r="T49">
-        <v>2.166158308971837</v>
+        <v>2.207815199528988</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2167098985004266</v>
+        <v>0.2121951089483344</v>
       </c>
       <c r="W49">
-        <v>0.1149869869001374</v>
+        <v>0.1156497580063845</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.9029579104184442</v>
+        <v>0.8841462872847267</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.135164709449964</v>
+        <v>0.136174709449964</v>
       </c>
       <c r="C50">
-        <v>49.11870046307142</v>
+        <v>45.88521284313927</v>
       </c>
       <c r="D50">
-        <v>115.5443004630714</v>
+        <v>114.2530128431393</v>
       </c>
       <c r="E50">
-        <v>87.1056</v>
+        <v>89.0478</v>
       </c>
       <c r="F50">
-        <v>93.2256</v>
+        <v>95.1678</v>
       </c>
       <c r="G50">
         <v>26.8</v>
@@ -5393,37 +5393,37 @@
         <v>12.1</v>
       </c>
       <c r="M50">
-        <v>13.68551808</v>
+        <v>13.97063304</v>
       </c>
       <c r="N50">
-        <v>-1.58551808</v>
+        <v>-1.87063304</v>
       </c>
       <c r="O50">
-        <v>-0.3805243392</v>
+        <v>-0.4489519295999999</v>
       </c>
       <c r="P50">
-        <v>-1.2049937408</v>
+        <v>-1.4216811104</v>
       </c>
       <c r="Q50">
-        <v>7.7950062592</v>
+        <v>7.5783188896</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1531785107824989</v>
+        <v>0.1552839717782342</v>
       </c>
       <c r="T50">
-        <v>2.207815199528987</v>
+        <v>2.251105693637399</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2121951089483344</v>
+        <v>0.2078645965208174</v>
       </c>
       <c r="W50">
-        <v>0.1156497580063845</v>
+        <v>0.116285477230744</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8841462872847267</v>
+        <v>0.8661024855034056</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.136174709449964</v>
+        <v>0.137184709449964</v>
       </c>
       <c r="C51">
-        <v>45.88521284313927</v>
+        <v>42.68026830232795</v>
       </c>
       <c r="D51">
-        <v>114.2530128431393</v>
+        <v>112.9902683023279</v>
       </c>
       <c r="E51">
-        <v>89.0478</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F51">
-        <v>95.1678</v>
+        <v>97.11</v>
       </c>
       <c r="G51">
         <v>26.8</v>
@@ -5475,37 +5475,37 @@
         <v>12.1</v>
       </c>
       <c r="M51">
-        <v>13.97063304</v>
+        <v>14.255748</v>
       </c>
       <c r="N51">
-        <v>-1.87063304</v>
+        <v>-2.155747999999999</v>
       </c>
       <c r="O51">
-        <v>-0.4489519295999999</v>
+        <v>-0.5173795199999998</v>
       </c>
       <c r="P51">
-        <v>-1.4216811104</v>
+        <v>-1.638368479999999</v>
       </c>
       <c r="Q51">
-        <v>7.5783188896</v>
+        <v>7.36163152</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1552839717782342</v>
+        <v>0.1574736512137989</v>
       </c>
       <c r="T51">
-        <v>2.251105693637399</v>
+        <v>2.296127807510147</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2078645965208174</v>
+        <v>0.203707304590401</v>
       </c>
       <c r="W51">
-        <v>0.116285477230744</v>
+        <v>0.1168957676861292</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8661024855034056</v>
+        <v>0.8487804357933376</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.137184709449964</v>
+        <v>0.138194709449964</v>
       </c>
       <c r="C52">
-        <v>42.68026830232795</v>
+        <v>39.50293079646079</v>
       </c>
       <c r="D52">
-        <v>112.9902683023279</v>
+        <v>111.7551307964608</v>
       </c>
       <c r="E52">
-        <v>90.98999999999999</v>
+        <v>92.93219999999999</v>
       </c>
       <c r="F52">
-        <v>97.11</v>
+        <v>99.0522</v>
       </c>
       <c r="G52">
         <v>26.8</v>
@@ -5557,37 +5557,37 @@
         <v>12.1</v>
       </c>
       <c r="M52">
-        <v>14.255748</v>
+        <v>14.54086296</v>
       </c>
       <c r="N52">
-        <v>-2.155747999999999</v>
+        <v>-2.44086296</v>
       </c>
       <c r="O52">
-        <v>-0.5173795199999998</v>
+        <v>-0.5858071104000001</v>
       </c>
       <c r="P52">
-        <v>-1.638368479999999</v>
+        <v>-1.8550558496</v>
       </c>
       <c r="Q52">
-        <v>7.36163152</v>
+        <v>7.1449441504</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1574736512137989</v>
+        <v>0.1597527053202029</v>
       </c>
       <c r="T52">
-        <v>2.296127807510147</v>
+        <v>2.342987558683823</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.203707304590401</v>
+        <v>0.1997130437160794</v>
       </c>
       <c r="W52">
-        <v>0.1168957676861292</v>
+        <v>0.1174821251824796</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8487804357933376</v>
+        <v>0.8321376821503309</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.138194709449964</v>
+        <v>0.139204709449964</v>
       </c>
       <c r="C53">
-        <v>39.50293079646079</v>
+        <v>36.35230476774014</v>
       </c>
       <c r="D53">
-        <v>111.7551307964608</v>
+        <v>110.5467047677401</v>
       </c>
       <c r="E53">
-        <v>92.93219999999999</v>
+        <v>94.87439999999999</v>
       </c>
       <c r="F53">
-        <v>99.0522</v>
+        <v>100.9944</v>
       </c>
       <c r="G53">
         <v>26.8</v>
@@ -5639,37 +5639,37 @@
         <v>12.1</v>
       </c>
       <c r="M53">
-        <v>14.54086296</v>
+        <v>14.82597792</v>
       </c>
       <c r="N53">
-        <v>-2.44086296</v>
+        <v>-2.72597792</v>
       </c>
       <c r="O53">
-        <v>-0.5858071104000001</v>
+        <v>-0.6542347008</v>
       </c>
       <c r="P53">
-        <v>-1.8550558496</v>
+        <v>-2.0717432192</v>
       </c>
       <c r="Q53">
-        <v>7.1449441504</v>
+        <v>6.9282567808</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1597527053202029</v>
+        <v>0.1621267200143738</v>
       </c>
       <c r="T53">
-        <v>2.342987558683823</v>
+        <v>2.391799799489737</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1997130437160794</v>
+        <v>0.195872408260001</v>
       </c>
       <c r="W53">
-        <v>0.1174821251824796</v>
+        <v>0.1180459304674319</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8321376821503309</v>
+        <v>0.8161350344166707</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.139204709449964</v>
+        <v>0.140214709449964</v>
       </c>
       <c r="C54">
-        <v>36.35230476774014</v>
+        <v>33.22753297923524</v>
       </c>
       <c r="D54">
-        <v>110.5467047677401</v>
+        <v>109.3641329792352</v>
       </c>
       <c r="E54">
-        <v>94.87439999999999</v>
+        <v>96.81659999999999</v>
       </c>
       <c r="F54">
-        <v>100.9944</v>
+        <v>102.9366</v>
       </c>
       <c r="G54">
         <v>26.8</v>
@@ -5721,37 +5721,37 @@
         <v>12.1</v>
       </c>
       <c r="M54">
-        <v>14.82597792</v>
+        <v>15.11109288</v>
       </c>
       <c r="N54">
-        <v>-2.72597792</v>
+        <v>-3.01109288</v>
       </c>
       <c r="O54">
-        <v>-0.6542347008</v>
+        <v>-0.7226622911999999</v>
       </c>
       <c r="P54">
-        <v>-2.0717432192</v>
+        <v>-2.2884305888</v>
       </c>
       <c r="Q54">
-        <v>6.9282567808</v>
+        <v>6.7115694112</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1621267200143738</v>
+        <v>0.1646017566104243</v>
       </c>
       <c r="T54">
-        <v>2.391799799489737</v>
+        <v>2.442689156925688</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.195872408260001</v>
+        <v>0.1921767024437745</v>
       </c>
       <c r="W54">
-        <v>0.1180459304674319</v>
+        <v>0.1185884600812539</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8161350344166707</v>
+        <v>0.800736260182394</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.140214709449964</v>
+        <v>0.1720875746487632</v>
       </c>
       <c r="C55">
-        <v>33.22753297923524</v>
+        <v>3.68366054451279</v>
       </c>
       <c r="D55">
-        <v>109.3641329792352</v>
+        <v>81.76246054451281</v>
       </c>
       <c r="E55">
-        <v>96.81659999999999</v>
+        <v>98.75880000000001</v>
       </c>
       <c r="F55">
-        <v>102.9366</v>
+        <v>104.8788</v>
       </c>
       <c r="G55">
         <v>26.8</v>
@@ -5803,45 +5803,45 @@
         <v>12.1</v>
       </c>
       <c r="M55">
-        <v>15.11109288</v>
+        <v>21.05966304</v>
       </c>
       <c r="N55">
-        <v>-3.01109288</v>
+        <v>-8.959663040000002</v>
       </c>
       <c r="O55">
-        <v>-0.7226622911999999</v>
+        <v>-2.150319129600001</v>
       </c>
       <c r="P55">
-        <v>-2.2884305888</v>
+        <v>-6.809343910400002</v>
       </c>
       <c r="Q55">
-        <v>6.7115694112</v>
+        <v>2.190656089599998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1646017566104243</v>
+        <v>0.1708862843602145</v>
       </c>
       <c r="T55">
-        <v>2.442689156925688</v>
+        <v>2.571905662041439</v>
       </c>
       <c r="U55">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1921767024437745</v>
+        <v>0.137893944194845</v>
       </c>
       <c r="W55">
-        <v>0.1185884600812539</v>
+        <v>0.1731108960056751</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.800736260182394</v>
+        <v>0.5745581008118541</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1720875746487632</v>
+        <v>0.1736375746487633</v>
       </c>
       <c r="C56">
-        <v>3.68366054451279</v>
+        <v>0.750110276861065</v>
       </c>
       <c r="D56">
-        <v>81.76246054451281</v>
+        <v>80.77111027686108</v>
       </c>
       <c r="E56">
-        <v>98.75880000000001</v>
+        <v>100.701</v>
       </c>
       <c r="F56">
-        <v>104.8788</v>
+        <v>106.821</v>
       </c>
       <c r="G56">
         <v>26.8</v>
@@ -5885,37 +5885,37 @@
         <v>12.1</v>
       </c>
       <c r="M56">
-        <v>21.05966304</v>
+        <v>21.4496568</v>
       </c>
       <c r="N56">
-        <v>-8.959663040000002</v>
+        <v>-9.349656800000002</v>
       </c>
       <c r="O56">
-        <v>-2.150319129600001</v>
+        <v>-2.243917632</v>
       </c>
       <c r="P56">
-        <v>-6.809343910400002</v>
+        <v>-7.105739168000001</v>
       </c>
       <c r="Q56">
-        <v>2.190656089599998</v>
+        <v>1.894260831999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1708862843602145</v>
+        <v>0.1736659795682193</v>
       </c>
       <c r="T56">
-        <v>2.571905662041439</v>
+        <v>2.629059121197915</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.137893944194845</v>
+        <v>0.1353867815731205</v>
       </c>
       <c r="W56">
-        <v>0.1731108960056751</v>
+        <v>0.1736143342601174</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5745581008118541</v>
+        <v>0.5641115898880023</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1736375746487633</v>
+        <v>0.1751875746487632</v>
       </c>
       <c r="C57">
-        <v>0.750110276861065</v>
+        <v>-2.159688205983883</v>
       </c>
       <c r="D57">
-        <v>80.77111027686108</v>
+        <v>79.80351179401613</v>
       </c>
       <c r="E57">
-        <v>100.701</v>
+        <v>102.6432</v>
       </c>
       <c r="F57">
-        <v>106.821</v>
+        <v>108.7632</v>
       </c>
       <c r="G57">
         <v>26.8</v>
@@ -5967,37 +5967,37 @@
         <v>12.1</v>
       </c>
       <c r="M57">
-        <v>21.4496568</v>
+        <v>21.83965056</v>
       </c>
       <c r="N57">
-        <v>-9.349656800000002</v>
+        <v>-9.739650560000001</v>
       </c>
       <c r="O57">
-        <v>-2.243917632</v>
+        <v>-2.3375161344</v>
       </c>
       <c r="P57">
-        <v>-7.105739168000001</v>
+        <v>-7.402134425600001</v>
       </c>
       <c r="Q57">
-        <v>1.894260831999999</v>
+        <v>1.597865574399999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1736659795682193</v>
+        <v>0.1765720245584061</v>
       </c>
       <c r="T57">
-        <v>2.629059121197915</v>
+        <v>2.688810464861504</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1353867815731205</v>
+        <v>0.1329691604736005</v>
       </c>
       <c r="W57">
-        <v>0.1736143342601174</v>
+        <v>0.174099792576901</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5641115898880023</v>
+        <v>0.5540381686400022</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1751875746487632</v>
+        <v>0.1767375746487632</v>
       </c>
       <c r="C58">
-        <v>-2.159688205983883</v>
+        <v>-5.046578403679504</v>
       </c>
       <c r="D58">
-        <v>79.80351179401613</v>
+        <v>78.85882159632051</v>
       </c>
       <c r="E58">
-        <v>102.6432</v>
+        <v>104.5854</v>
       </c>
       <c r="F58">
-        <v>108.7632</v>
+        <v>110.7054</v>
       </c>
       <c r="G58">
         <v>26.8</v>
@@ -6049,37 +6049,37 @@
         <v>12.1</v>
       </c>
       <c r="M58">
-        <v>21.83965056</v>
+        <v>22.22964432</v>
       </c>
       <c r="N58">
-        <v>-9.739650560000001</v>
+        <v>-10.12964432</v>
       </c>
       <c r="O58">
-        <v>-2.3375161344</v>
+        <v>-2.4311146368</v>
       </c>
       <c r="P58">
-        <v>-7.402134425600001</v>
+        <v>-7.6985296832</v>
       </c>
       <c r="Q58">
-        <v>1.597865574399999</v>
+        <v>1.3014703168</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1765720245584061</v>
+        <v>0.1796132344318574</v>
       </c>
       <c r="T58">
-        <v>2.688810464861504</v>
+        <v>2.751340940788516</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1329691604736005</v>
+        <v>0.13063636818459</v>
       </c>
       <c r="W58">
-        <v>0.174099792576901</v>
+        <v>0.1745682172685343</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5540381686400022</v>
+        <v>0.5443182007691251</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1767375746487632</v>
+        <v>0.1782875746487632</v>
       </c>
       <c r="C59">
-        <v>-5.046578403679504</v>
+        <v>-7.911364342763548</v>
       </c>
       <c r="D59">
-        <v>78.85882159632051</v>
+        <v>77.93623565723647</v>
       </c>
       <c r="E59">
-        <v>104.5854</v>
+        <v>106.5276</v>
       </c>
       <c r="F59">
-        <v>110.7054</v>
+        <v>112.6476</v>
       </c>
       <c r="G59">
         <v>26.8</v>
@@ -6131,37 +6131,37 @@
         <v>12.1</v>
       </c>
       <c r="M59">
-        <v>22.22964432</v>
+        <v>22.61963808</v>
       </c>
       <c r="N59">
-        <v>-10.12964432</v>
+        <v>-10.51963808</v>
       </c>
       <c r="O59">
-        <v>-2.4311146368</v>
+        <v>-2.5247131392</v>
       </c>
       <c r="P59">
-        <v>-7.6985296832</v>
+        <v>-7.994924940800001</v>
       </c>
       <c r="Q59">
-        <v>1.3014703168</v>
+        <v>1.005075059199999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1796132344318574</v>
+        <v>0.1827992638230921</v>
       </c>
       <c r="T59">
-        <v>2.751340940788516</v>
+        <v>2.816849058426338</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.13063636818459</v>
+        <v>0.1283840170089936</v>
       </c>
       <c r="W59">
-        <v>0.1745682172685343</v>
+        <v>0.1750204893845941</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5443182007691251</v>
+        <v>0.5349334042041402</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1782875746487632</v>
+        <v>0.1798375746487633</v>
       </c>
       <c r="C60">
-        <v>-7.911364342763534</v>
+        <v>-10.75481285897453</v>
       </c>
       <c r="D60">
-        <v>77.93623565723647</v>
+        <v>77.03498714102547</v>
       </c>
       <c r="E60">
-        <v>106.5276</v>
+        <v>108.4698</v>
       </c>
       <c r="F60">
-        <v>112.6476</v>
+        <v>114.5898</v>
       </c>
       <c r="G60">
         <v>26.8</v>
@@ -6213,37 +6213,37 @@
         <v>12.1</v>
       </c>
       <c r="M60">
-        <v>22.61963808</v>
+        <v>23.00963184</v>
       </c>
       <c r="N60">
-        <v>-10.51963808</v>
+        <v>-10.90963184</v>
       </c>
       <c r="O60">
-        <v>-2.5247131392</v>
+        <v>-2.6183116416</v>
       </c>
       <c r="P60">
-        <v>-7.994924940800001</v>
+        <v>-8.291320198399999</v>
       </c>
       <c r="Q60">
-        <v>1.005075059199999</v>
+        <v>0.7086798016000007</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1827992638230921</v>
+        <v>0.1861407092821919</v>
       </c>
       <c r="T60">
-        <v>2.816849058426338</v>
+        <v>2.885552693997712</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1283840170089936</v>
+        <v>0.1262080167207056</v>
       </c>
       <c r="W60">
-        <v>0.1750204893845941</v>
+        <v>0.1754574302424823</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5349334042041402</v>
+        <v>0.5258667363362735</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1798375746487633</v>
+        <v>0.1813875746487632</v>
       </c>
       <c r="C61">
-        <v>-10.75481285897453</v>
+        <v>-13.57765572302679</v>
       </c>
       <c r="D61">
-        <v>77.03498714102547</v>
+        <v>76.15434427697321</v>
       </c>
       <c r="E61">
-        <v>108.4698</v>
+        <v>110.412</v>
       </c>
       <c r="F61">
-        <v>114.5898</v>
+        <v>116.532</v>
       </c>
       <c r="G61">
         <v>26.8</v>
@@ -6295,37 +6295,37 @@
         <v>12.1</v>
       </c>
       <c r="M61">
-        <v>23.00963184</v>
+        <v>23.3996256</v>
       </c>
       <c r="N61">
-        <v>-10.90963184</v>
+        <v>-11.2996256</v>
       </c>
       <c r="O61">
-        <v>-2.6183116416</v>
+        <v>-2.711910144</v>
       </c>
       <c r="P61">
-        <v>-8.291320198399999</v>
+        <v>-8.587715456</v>
       </c>
       <c r="Q61">
-        <v>0.7086798016000007</v>
+        <v>0.4122845440000003</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1861407092821919</v>
+        <v>0.1896492270142467</v>
       </c>
       <c r="T61">
-        <v>2.885552693997712</v>
+        <v>2.957691511347654</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1262080167207056</v>
+        <v>0.1241045497753605</v>
       </c>
       <c r="W61">
-        <v>0.1754574302424823</v>
+        <v>0.1758798064051076</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5258667363362735</v>
+        <v>0.5171022907306688</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1813875746487632</v>
+        <v>0.1829375746487632</v>
       </c>
       <c r="C62">
-        <v>-13.57765572302679</v>
+        <v>-16.38059162222605</v>
       </c>
       <c r="D62">
-        <v>76.15434427697321</v>
+        <v>75.29360837777395</v>
       </c>
       <c r="E62">
-        <v>110.412</v>
+        <v>112.3542</v>
       </c>
       <c r="F62">
-        <v>116.532</v>
+        <v>118.4742</v>
       </c>
       <c r="G62">
         <v>26.8</v>
@@ -6377,37 +6377,37 @@
         <v>12.1</v>
       </c>
       <c r="M62">
-        <v>23.3996256</v>
+        <v>23.78961936</v>
       </c>
       <c r="N62">
-        <v>-11.2996256</v>
+        <v>-11.68961936</v>
       </c>
       <c r="O62">
-        <v>-2.711910144</v>
+        <v>-2.805508646399999</v>
       </c>
       <c r="P62">
-        <v>-8.587715456</v>
+        <v>-8.884110713599998</v>
       </c>
       <c r="Q62">
-        <v>0.4122845440000003</v>
+        <v>0.1158892864000016</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1896492270142467</v>
+        <v>0.1933376687325607</v>
       </c>
       <c r="T62">
-        <v>2.957691511347654</v>
+        <v>3.033529755228364</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1241045497753605</v>
+        <v>0.122070048959371</v>
       </c>
       <c r="W62">
-        <v>0.1758798064051076</v>
+        <v>0.1762883341689583</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5171022907306688</v>
+        <v>0.5086252039973792</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1829375746487632</v>
+        <v>0.1844875746487633</v>
       </c>
       <c r="C63">
-        <v>-16.38059162222605</v>
+        <v>-19.16428800920316</v>
       </c>
       <c r="D63">
-        <v>75.29360837777395</v>
+        <v>74.45211199079684</v>
       </c>
       <c r="E63">
-        <v>112.3542</v>
+        <v>114.2964</v>
       </c>
       <c r="F63">
-        <v>118.4742</v>
+        <v>120.4164</v>
       </c>
       <c r="G63">
         <v>26.8</v>
@@ -6459,37 +6459,37 @@
         <v>12.1</v>
       </c>
       <c r="M63">
-        <v>23.78961936</v>
+        <v>24.17961312</v>
       </c>
       <c r="N63">
-        <v>-11.68961936</v>
+        <v>-12.07961312</v>
       </c>
       <c r="O63">
-        <v>-2.805508646399999</v>
+        <v>-2.899107148799999</v>
       </c>
       <c r="P63">
-        <v>-8.884110713599998</v>
+        <v>-9.180505971199999</v>
       </c>
       <c r="Q63">
-        <v>0.1158892864000016</v>
+        <v>-0.1805059711999988</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1933376687325607</v>
+        <v>0.1972202389623649</v>
       </c>
       <c r="T63">
-        <v>3.033529755228364</v>
+        <v>3.11335948562911</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.122070048959371</v>
+        <v>0.1201011772019618</v>
       </c>
       <c r="W63">
-        <v>0.1762883341689583</v>
+        <v>0.1766836836178461</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5086252039973792</v>
+        <v>0.5004215716748408</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1844875746487633</v>
+        <v>0.2087747013248094</v>
       </c>
       <c r="C64">
-        <v>-19.16428800920316</v>
+        <v>-32.20163259618937</v>
       </c>
       <c r="D64">
-        <v>74.45211199079684</v>
+        <v>63.35696740381062</v>
       </c>
       <c r="E64">
-        <v>114.2964</v>
+        <v>116.2386</v>
       </c>
       <c r="F64">
-        <v>120.4164</v>
+        <v>122.3586</v>
       </c>
       <c r="G64">
         <v>26.8</v>
@@ -6541,45 +6541,45 @@
         <v>12.1</v>
       </c>
       <c r="M64">
-        <v>24.17961312</v>
+        <v>28.85215788</v>
       </c>
       <c r="N64">
-        <v>-12.07961312</v>
+        <v>-16.75215788</v>
       </c>
       <c r="O64">
-        <v>-2.899107148799999</v>
+        <v>-4.0205178912</v>
       </c>
       <c r="P64">
-        <v>-9.180505971199999</v>
+        <v>-12.7316399888</v>
       </c>
       <c r="Q64">
-        <v>-0.1805059711999988</v>
+        <v>-3.731639988799998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1972202389623649</v>
+        <v>0.2031697769776886</v>
       </c>
       <c r="T64">
-        <v>3.11335948562911</v>
+        <v>3.235688249221425</v>
       </c>
       <c r="U64">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1201011772019618</v>
+        <v>0.1006510505064518</v>
       </c>
       <c r="W64">
-        <v>0.1766836836178461</v>
+        <v>0.2120664822905787</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.5004215716748408</v>
+        <v>0.4193793771102157</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2087747013248094</v>
+        <v>0.2106747013248094</v>
       </c>
       <c r="C65">
-        <v>-32.20163259618937</v>
+        <v>-34.87395211786233</v>
       </c>
       <c r="D65">
-        <v>63.35696740381062</v>
+        <v>62.62684788213767</v>
       </c>
       <c r="E65">
-        <v>116.2386</v>
+        <v>118.1808</v>
       </c>
       <c r="F65">
-        <v>122.3586</v>
+        <v>124.3008</v>
       </c>
       <c r="G65">
         <v>26.8</v>
@@ -6623,37 +6623,37 @@
         <v>12.1</v>
       </c>
       <c r="M65">
-        <v>28.85215788</v>
+        <v>29.31012864</v>
       </c>
       <c r="N65">
-        <v>-16.75215788</v>
+        <v>-17.21012864</v>
       </c>
       <c r="O65">
-        <v>-4.0205178912</v>
+        <v>-4.130430873599999</v>
       </c>
       <c r="P65">
-        <v>-12.7316399888</v>
+        <v>-13.0796977664</v>
       </c>
       <c r="Q65">
-        <v>-3.731639988799998</v>
+        <v>-4.079697766399999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2031697769776886</v>
+        <v>0.2075411596715133</v>
       </c>
       <c r="T65">
-        <v>3.235688249221425</v>
+        <v>3.325568478366465</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1006510505064518</v>
+        <v>0.09907837784228847</v>
       </c>
       <c r="W65">
-        <v>0.2120664822905787</v>
+        <v>0.2124373185047884</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4193793771102157</v>
+        <v>0.4128265743428686</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2106747013248094</v>
+        <v>0.2125747013248094</v>
       </c>
       <c r="C66">
-        <v>-34.87395211786233</v>
+        <v>-37.5296356979907</v>
       </c>
       <c r="D66">
-        <v>62.62684788213767</v>
+        <v>61.91336430200931</v>
       </c>
       <c r="E66">
-        <v>118.1808</v>
+        <v>120.123</v>
       </c>
       <c r="F66">
-        <v>124.3008</v>
+        <v>126.243</v>
       </c>
       <c r="G66">
         <v>26.8</v>
@@ -6705,37 +6705,37 @@
         <v>12.1</v>
       </c>
       <c r="M66">
-        <v>29.31012864</v>
+        <v>29.7680994</v>
       </c>
       <c r="N66">
-        <v>-17.21012864</v>
+        <v>-17.6680994</v>
       </c>
       <c r="O66">
-        <v>-4.130430873599999</v>
+        <v>-4.240343856000001</v>
       </c>
       <c r="P66">
-        <v>-13.0796977664</v>
+        <v>-13.427755544</v>
       </c>
       <c r="Q66">
-        <v>-4.079697766399999</v>
+        <v>-4.427755544000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2075411596715133</v>
+        <v>0.212162335662128</v>
       </c>
       <c r="T66">
-        <v>3.325568478366465</v>
+        <v>3.420584720605507</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09907837784228847</v>
+        <v>0.09755409510625324</v>
       </c>
       <c r="W66">
-        <v>0.2124373185047884</v>
+        <v>0.2127967443739455</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4128265743428686</v>
+        <v>0.4064753962760551</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2125747013248094</v>
+        <v>0.2144747013248094</v>
       </c>
       <c r="C67">
-        <v>-37.5296356979907</v>
+        <v>-40.16924551256209</v>
       </c>
       <c r="D67">
-        <v>61.91336430200931</v>
+        <v>61.21595448743793</v>
       </c>
       <c r="E67">
-        <v>120.123</v>
+        <v>122.0652</v>
       </c>
       <c r="F67">
-        <v>126.243</v>
+        <v>128.1852</v>
       </c>
       <c r="G67">
         <v>26.8</v>
@@ -6787,37 +6787,37 @@
         <v>12.1</v>
       </c>
       <c r="M67">
-        <v>29.7680994</v>
+        <v>30.22607016</v>
       </c>
       <c r="N67">
-        <v>-17.6680994</v>
+        <v>-18.12607016</v>
       </c>
       <c r="O67">
-        <v>-4.240343856000001</v>
+        <v>-4.3502568384</v>
       </c>
       <c r="P67">
-        <v>-13.427755544</v>
+        <v>-13.7758133216</v>
       </c>
       <c r="Q67">
-        <v>-4.427755544000002</v>
+        <v>-4.775813321600001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.212162335662128</v>
+        <v>0.2170553455345435</v>
       </c>
       <c r="T67">
-        <v>3.420584720605507</v>
+        <v>3.521190153564492</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09755409510625324</v>
+        <v>0.09607600275615849</v>
       </c>
       <c r="W67">
-        <v>0.2127967443739455</v>
+        <v>0.2131452785500978</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4064753962760551</v>
+        <v>0.4003166781506604</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2144747013248094</v>
+        <v>0.2163747013248093</v>
       </c>
       <c r="C68">
-        <v>-40.16924551256209</v>
+        <v>-42.79331868966732</v>
       </c>
       <c r="D68">
-        <v>61.21595448743793</v>
+        <v>60.53408131033267</v>
       </c>
       <c r="E68">
-        <v>122.0652</v>
+        <v>124.0074</v>
       </c>
       <c r="F68">
-        <v>128.1852</v>
+        <v>130.1274</v>
       </c>
       <c r="G68">
         <v>26.8</v>
@@ -6869,37 +6869,37 @@
         <v>12.1</v>
       </c>
       <c r="M68">
-        <v>30.22607016</v>
+        <v>30.68404092</v>
       </c>
       <c r="N68">
-        <v>-18.12607016</v>
+        <v>-18.58404092</v>
       </c>
       <c r="O68">
-        <v>-4.3502568384</v>
+        <v>-4.4601698208</v>
       </c>
       <c r="P68">
-        <v>-13.7758133216</v>
+        <v>-14.1238710992</v>
       </c>
       <c r="Q68">
-        <v>-4.775813321600001</v>
+        <v>-5.123871099199999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2170553455345435</v>
+        <v>0.2222449014598327</v>
       </c>
       <c r="T68">
-        <v>3.521190153564492</v>
+        <v>3.627892885490689</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09607600275615849</v>
+        <v>0.09464203256576807</v>
       </c>
       <c r="W68">
-        <v>0.2131452785500978</v>
+        <v>0.2134834087209919</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4003166781506604</v>
+        <v>0.3943418023573669</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2163747013248093</v>
+        <v>0.2182747013248094</v>
       </c>
       <c r="C69">
-        <v>-42.79331868966732</v>
+        <v>-45.40236868915241</v>
       </c>
       <c r="D69">
-        <v>60.53408131033267</v>
+        <v>59.8672313108476</v>
       </c>
       <c r="E69">
-        <v>124.0074</v>
+        <v>125.9496</v>
       </c>
       <c r="F69">
-        <v>130.1274</v>
+        <v>132.0696</v>
       </c>
       <c r="G69">
         <v>26.8</v>
@@ -6951,37 +6951,37 @@
         <v>12.1</v>
       </c>
       <c r="M69">
-        <v>30.68404092</v>
+        <v>31.14201168</v>
       </c>
       <c r="N69">
-        <v>-18.58404092</v>
+        <v>-19.04201168</v>
       </c>
       <c r="O69">
-        <v>-4.4601698208</v>
+        <v>-4.5700828032</v>
       </c>
       <c r="P69">
-        <v>-14.1238710992</v>
+        <v>-14.4719288768</v>
       </c>
       <c r="Q69">
-        <v>-5.123871099199999</v>
+        <v>-5.471928876800002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2222449014598327</v>
+        <v>0.2277588046304525</v>
       </c>
       <c r="T69">
-        <v>3.627892885490689</v>
+        <v>3.741264538162274</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09464203256576807</v>
+        <v>0.09325023796921265</v>
       </c>
       <c r="W69">
-        <v>0.2134834087209919</v>
+        <v>0.2138115938868597</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3943418023573669</v>
+        <v>0.3885426582050527</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2182747013248094</v>
+        <v>0.2201747013248094</v>
       </c>
       <c r="C70">
-        <v>-45.40236868915241</v>
+        <v>-47.99688659207304</v>
       </c>
       <c r="D70">
-        <v>59.8672313108476</v>
+        <v>59.21491340792699</v>
       </c>
       <c r="E70">
-        <v>125.9496</v>
+        <v>127.8918</v>
       </c>
       <c r="F70">
-        <v>132.0696</v>
+        <v>134.0118</v>
       </c>
       <c r="G70">
         <v>26.8</v>
@@ -7033,37 +7033,37 @@
         <v>12.1</v>
       </c>
       <c r="M70">
-        <v>31.14201168</v>
+        <v>31.59998244000001</v>
       </c>
       <c r="N70">
-        <v>-19.04201168</v>
+        <v>-19.49998244</v>
       </c>
       <c r="O70">
-        <v>-4.5700828032</v>
+        <v>-4.679995785600001</v>
       </c>
       <c r="P70">
-        <v>-14.4719288768</v>
+        <v>-14.8199866544</v>
       </c>
       <c r="Q70">
-        <v>-5.471928876800002</v>
+        <v>-5.819986654400003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2277588046304525</v>
+        <v>0.2336284434894994</v>
       </c>
       <c r="T70">
-        <v>3.741264538162274</v>
+        <v>3.861950491006218</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09325023796921265</v>
+        <v>0.09189878524502115</v>
       </c>
       <c r="W70">
-        <v>0.2138115938868597</v>
+        <v>0.214130266439224</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3885426582050527</v>
+        <v>0.3829116051875882</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2201747013248094</v>
+        <v>0.2220747013248094</v>
       </c>
       <c r="C71">
-        <v>-47.99688659207304</v>
+        <v>-50.57734230675865</v>
       </c>
       <c r="D71">
-        <v>59.21491340792699</v>
+        <v>58.57665769324135</v>
       </c>
       <c r="E71">
-        <v>127.8918</v>
+        <v>129.834</v>
       </c>
       <c r="F71">
-        <v>134.0118</v>
+        <v>135.954</v>
       </c>
       <c r="G71">
         <v>26.8</v>
@@ -7115,37 +7115,37 @@
         <v>12.1</v>
       </c>
       <c r="M71">
-        <v>31.59998244000001</v>
+        <v>32.0579532</v>
       </c>
       <c r="N71">
-        <v>-19.49998244</v>
+        <v>-19.9579532</v>
       </c>
       <c r="O71">
-        <v>-4.679995785600001</v>
+        <v>-4.789908767999999</v>
       </c>
       <c r="P71">
-        <v>-14.8199866544</v>
+        <v>-15.168044432</v>
       </c>
       <c r="Q71">
-        <v>-5.819986654400003</v>
+        <v>-6.168044431999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2336284434894994</v>
+        <v>0.239889391605816</v>
       </c>
       <c r="T71">
-        <v>3.861950491006218</v>
+        <v>3.990682174039759</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09189878524502115</v>
+        <v>0.09058594545580659</v>
       </c>
       <c r="W71">
-        <v>0.214130266439224</v>
+        <v>0.2144398340615208</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3829116051875882</v>
+        <v>0.3774414393991942</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2220747013248094</v>
+        <v>0.2239747013248094</v>
       </c>
       <c r="C72">
-        <v>-50.57734230675865</v>
+        <v>-53.14418569770937</v>
       </c>
       <c r="D72">
-        <v>58.57665769324135</v>
+        <v>57.95201430229065</v>
       </c>
       <c r="E72">
-        <v>129.834</v>
+        <v>131.7762</v>
       </c>
       <c r="F72">
-        <v>135.954</v>
+        <v>137.8962</v>
       </c>
       <c r="G72">
         <v>26.8</v>
@@ -7197,37 +7197,37 @@
         <v>12.1</v>
       </c>
       <c r="M72">
-        <v>32.0579532</v>
+        <v>32.51592396000001</v>
       </c>
       <c r="N72">
-        <v>-19.9579532</v>
+        <v>-20.41592396000001</v>
       </c>
       <c r="O72">
-        <v>-4.789908767999999</v>
+        <v>-4.899821750400002</v>
       </c>
       <c r="P72">
-        <v>-15.168044432</v>
+        <v>-15.51610220960001</v>
       </c>
       <c r="Q72">
-        <v>-6.168044431999999</v>
+        <v>-6.516102209600007</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.239889391605816</v>
+        <v>0.2465821292473959</v>
       </c>
       <c r="T72">
-        <v>3.990682174039759</v>
+        <v>4.128291904179061</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09058594545580659</v>
+        <v>0.08931008706910507</v>
       </c>
       <c r="W72">
-        <v>0.2144398340615208</v>
+        <v>0.214740681469105</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3774414393991942</v>
+        <v>0.3721253627879377</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2239747013248094</v>
+        <v>0.2258747013248094</v>
       </c>
       <c r="C73">
-        <v>-53.14418569770935</v>
+        <v>-55.69784764302582</v>
       </c>
       <c r="D73">
-        <v>57.95201430229065</v>
+        <v>57.34055235697418</v>
       </c>
       <c r="E73">
-        <v>131.7762</v>
+        <v>133.7184</v>
       </c>
       <c r="F73">
-        <v>137.8962</v>
+        <v>139.8384</v>
       </c>
       <c r="G73">
         <v>26.8</v>
@@ -7279,37 +7279,37 @@
         <v>12.1</v>
       </c>
       <c r="M73">
-        <v>32.51592396</v>
+        <v>32.97389472</v>
       </c>
       <c r="N73">
-        <v>-20.41592396</v>
+        <v>-20.87389472</v>
       </c>
       <c r="O73">
-        <v>-4.8998217504</v>
+        <v>-5.0097347328</v>
       </c>
       <c r="P73">
-        <v>-15.5161022096</v>
+        <v>-15.8641599872</v>
       </c>
       <c r="Q73">
-        <v>-6.5161022096</v>
+        <v>-6.864159987200003</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2465821292473958</v>
+        <v>0.2537529195776599</v>
       </c>
       <c r="T73">
-        <v>4.12829190417906</v>
+        <v>4.275730900756884</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08931008706910508</v>
+        <v>0.08806966919314528</v>
       </c>
       <c r="W73">
-        <v>0.214740681469105</v>
+        <v>0.2150331720042563</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3721253627879378</v>
+        <v>0.3669569549714387</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2258747013248094</v>
+        <v>0.2277747013248094</v>
       </c>
       <c r="C74">
-        <v>-55.69784764302582</v>
+        <v>-58.23874102559546</v>
       </c>
       <c r="D74">
-        <v>57.34055235697418</v>
+        <v>56.74185897440454</v>
       </c>
       <c r="E74">
-        <v>133.7184</v>
+        <v>135.6606</v>
       </c>
       <c r="F74">
-        <v>139.8384</v>
+        <v>141.7806</v>
       </c>
       <c r="G74">
         <v>26.8</v>
@@ -7361,37 +7361,37 @@
         <v>12.1</v>
       </c>
       <c r="M74">
-        <v>32.97389472</v>
+        <v>33.43186548</v>
       </c>
       <c r="N74">
-        <v>-20.87389472</v>
+        <v>-21.33186548</v>
       </c>
       <c r="O74">
-        <v>-5.0097347328</v>
+        <v>-5.119647715199999</v>
       </c>
       <c r="P74">
-        <v>-15.8641599872</v>
+        <v>-16.2122177648</v>
       </c>
       <c r="Q74">
-        <v>-6.864159987200003</v>
+        <v>-7.212217764799998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2537529195776599</v>
+        <v>0.2614548795620177</v>
       </c>
       <c r="T74">
-        <v>4.275730900756884</v>
+        <v>4.434091304488619</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08806966919314528</v>
+        <v>0.08686323536858166</v>
       </c>
       <c r="W74">
-        <v>0.2150331720042563</v>
+        <v>0.2153176491000885</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3669569549714387</v>
+        <v>0.3619301473690902</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2277747013248094</v>
+        <v>0.2296747013248094</v>
       </c>
       <c r="C75">
-        <v>-58.23874102559546</v>
+        <v>-60.7672616628262</v>
       </c>
       <c r="D75">
-        <v>56.74185897440454</v>
+        <v>56.15553833717381</v>
       </c>
       <c r="E75">
-        <v>135.6606</v>
+        <v>137.6028</v>
       </c>
       <c r="F75">
-        <v>141.7806</v>
+        <v>143.7228</v>
       </c>
       <c r="G75">
         <v>26.8</v>
@@ -7443,37 +7443,37 @@
         <v>12.1</v>
       </c>
       <c r="M75">
-        <v>33.43186548</v>
+        <v>33.88983624</v>
       </c>
       <c r="N75">
-        <v>-21.33186548</v>
+        <v>-21.78983624</v>
       </c>
       <c r="O75">
-        <v>-5.119647715199999</v>
+        <v>-5.229560697599999</v>
       </c>
       <c r="P75">
-        <v>-16.2122177648</v>
+        <v>-16.5602755424</v>
       </c>
       <c r="Q75">
-        <v>-7.212217764799998</v>
+        <v>-7.560275542399999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2614548795620177</v>
+        <v>0.2697492980067107</v>
       </c>
       <c r="T75">
-        <v>4.434091304488619</v>
+        <v>4.604633277738182</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08686323536858166</v>
+        <v>0.08568940786360082</v>
       </c>
       <c r="W75">
-        <v>0.2153176491000885</v>
+        <v>0.2155944376257629</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3619301473690902</v>
+        <v>0.3570391994316701</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2296747013248094</v>
+        <v>0.2315747013248093</v>
       </c>
       <c r="C76">
-        <v>-60.7672616628262</v>
+        <v>-63.28378917932737</v>
       </c>
       <c r="D76">
-        <v>56.15553833717381</v>
+        <v>55.58121082067262</v>
       </c>
       <c r="E76">
-        <v>137.6028</v>
+        <v>139.545</v>
       </c>
       <c r="F76">
-        <v>143.7228</v>
+        <v>145.665</v>
       </c>
       <c r="G76">
         <v>26.8</v>
@@ -7525,37 +7525,37 @@
         <v>12.1</v>
       </c>
       <c r="M76">
-        <v>33.88983624</v>
+        <v>34.347807</v>
       </c>
       <c r="N76">
-        <v>-21.78983624</v>
+        <v>-22.24780699999999</v>
       </c>
       <c r="O76">
-        <v>-5.229560697599999</v>
+        <v>-5.339473679999998</v>
       </c>
       <c r="P76">
-        <v>-16.5602755424</v>
+        <v>-16.90833332</v>
       </c>
       <c r="Q76">
-        <v>-7.560275542399999</v>
+        <v>-7.908333319999997</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2697492980067107</v>
+        <v>0.2787072699269791</v>
       </c>
       <c r="T76">
-        <v>4.604633277738182</v>
+        <v>4.788818608847709</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08568940786360082</v>
+        <v>0.0845468824254195</v>
       </c>
       <c r="W76">
-        <v>0.2155944376257629</v>
+        <v>0.2158638451240861</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3570391994316701</v>
+        <v>0.3522786767725812</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2315747013248093</v>
+        <v>0.2334747013248094</v>
       </c>
       <c r="C77">
-        <v>-63.28378917932737</v>
+        <v>-65.78868782658144</v>
       </c>
       <c r="D77">
-        <v>55.58121082067262</v>
+        <v>55.01851217341857</v>
       </c>
       <c r="E77">
-        <v>139.545</v>
+        <v>141.4872</v>
       </c>
       <c r="F77">
-        <v>145.665</v>
+        <v>147.6072</v>
       </c>
       <c r="G77">
         <v>26.8</v>
@@ -7607,37 +7607,37 @@
         <v>12.1</v>
       </c>
       <c r="M77">
-        <v>34.347807</v>
+        <v>34.80577776000001</v>
       </c>
       <c r="N77">
-        <v>-22.24780699999999</v>
+        <v>-22.70577776</v>
       </c>
       <c r="O77">
-        <v>-5.339473679999998</v>
+        <v>-5.4493866624</v>
       </c>
       <c r="P77">
-        <v>-16.90833332</v>
+        <v>-17.2563910976</v>
       </c>
       <c r="Q77">
-        <v>-7.908333319999997</v>
+        <v>-8.256391097600002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2787072699269791</v>
+        <v>0.2884117395072699</v>
       </c>
       <c r="T77">
-        <v>4.788818608847709</v>
+        <v>4.988352717549698</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0845468824254195</v>
+        <v>0.08343442344613763</v>
       </c>
       <c r="W77">
-        <v>0.2158638451240861</v>
+        <v>0.2161261629514008</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3522786767725812</v>
+        <v>0.3476434310255735</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2334747013248094</v>
+        <v>0.2353747013248094</v>
       </c>
       <c r="C78">
-        <v>-65.78868782658144</v>
+        <v>-68.28230725332439</v>
       </c>
       <c r="D78">
-        <v>55.01851217341857</v>
+        <v>54.4670927466756</v>
       </c>
       <c r="E78">
-        <v>141.4872</v>
+        <v>143.4294</v>
       </c>
       <c r="F78">
-        <v>147.6072</v>
+        <v>149.5494</v>
       </c>
       <c r="G78">
         <v>26.8</v>
@@ -7689,37 +7689,37 @@
         <v>12.1</v>
       </c>
       <c r="M78">
-        <v>34.80577776000001</v>
+        <v>35.26374852</v>
       </c>
       <c r="N78">
-        <v>-22.70577776</v>
+        <v>-23.16374852</v>
       </c>
       <c r="O78">
-        <v>-5.4493866624</v>
+        <v>-5.559299644799999</v>
       </c>
       <c r="P78">
-        <v>-17.2563910976</v>
+        <v>-17.6044488752</v>
       </c>
       <c r="Q78">
-        <v>-8.256391097600002</v>
+        <v>-8.604448875199999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2884117395072699</v>
+        <v>0.2989600760075861</v>
       </c>
       <c r="T78">
-        <v>4.988352717549698</v>
+        <v>5.205237618312728</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08343442344613763</v>
+        <v>0.08235085950527871</v>
       </c>
       <c r="W78">
-        <v>0.2161261629514008</v>
+        <v>0.2163816673286553</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3476434310255735</v>
+        <v>0.3431285812719946</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2353747013248094</v>
+        <v>0.2372747013248094</v>
       </c>
       <c r="C79">
-        <v>-68.28230725332439</v>
+        <v>-70.76498323006001</v>
       </c>
       <c r="D79">
-        <v>54.4670927466756</v>
+        <v>53.92661676994</v>
       </c>
       <c r="E79">
-        <v>143.4294</v>
+        <v>145.3716</v>
       </c>
       <c r="F79">
-        <v>149.5494</v>
+        <v>151.4916</v>
       </c>
       <c r="G79">
         <v>26.8</v>
@@ -7771,37 +7771,37 @@
         <v>12.1</v>
       </c>
       <c r="M79">
-        <v>35.26374852</v>
+        <v>35.72171928</v>
       </c>
       <c r="N79">
-        <v>-23.16374852</v>
+        <v>-23.62171928</v>
       </c>
       <c r="O79">
-        <v>-5.559299644799999</v>
+        <v>-5.6692126272</v>
       </c>
       <c r="P79">
-        <v>-17.6044488752</v>
+        <v>-17.9525066528</v>
       </c>
       <c r="Q79">
-        <v>-8.604448875199999</v>
+        <v>-8.9525066528</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2989600760075861</v>
+        <v>0.3104673521897491</v>
       </c>
       <c r="T79">
-        <v>5.205237618312728</v>
+        <v>5.441839328236034</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08235085950527871</v>
+        <v>0.08129507925521104</v>
       </c>
       <c r="W79">
-        <v>0.2163816673286553</v>
+        <v>0.2166306203116213</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3431285812719946</v>
+        <v>0.3387294968967126</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2372747013248094</v>
+        <v>0.2391747013248094</v>
       </c>
       <c r="C80">
-        <v>-70.76498323006001</v>
+        <v>-73.23703833086135</v>
       </c>
       <c r="D80">
-        <v>53.92661676994</v>
+        <v>53.39676166913867</v>
       </c>
       <c r="E80">
-        <v>145.3716</v>
+        <v>147.3138</v>
       </c>
       <c r="F80">
-        <v>151.4916</v>
+        <v>153.4338</v>
       </c>
       <c r="G80">
         <v>26.8</v>
@@ -7853,37 +7853,37 @@
         <v>12.1</v>
       </c>
       <c r="M80">
-        <v>35.72171928</v>
+        <v>36.17969004</v>
       </c>
       <c r="N80">
-        <v>-23.62171928</v>
+        <v>-24.07969004</v>
       </c>
       <c r="O80">
-        <v>-5.6692126272</v>
+        <v>-5.7791256096</v>
       </c>
       <c r="P80">
-        <v>-17.9525066528</v>
+        <v>-18.3005644304</v>
       </c>
       <c r="Q80">
-        <v>-8.9525066528</v>
+        <v>-9.300564430400001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3104673521897491</v>
+        <v>0.32307055943688</v>
       </c>
       <c r="T80">
-        <v>5.441839328236034</v>
+        <v>5.700974534342512</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08129507925521104</v>
+        <v>0.08026602761906912</v>
       </c>
       <c r="W80">
-        <v>0.2166306203116213</v>
+        <v>0.2168732706874235</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3387294968967126</v>
+        <v>0.3344417817461214</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2391747013248094</v>
+        <v>0.2410747013248093</v>
       </c>
       <c r="C81">
-        <v>-73.23703833086135</v>
+        <v>-75.69878257536953</v>
       </c>
       <c r="D81">
-        <v>53.39676166913867</v>
+        <v>52.87721742463047</v>
       </c>
       <c r="E81">
-        <v>147.3138</v>
+        <v>149.256</v>
       </c>
       <c r="F81">
-        <v>153.4338</v>
+        <v>155.376</v>
       </c>
       <c r="G81">
         <v>26.8</v>
@@ -7935,37 +7935,37 @@
         <v>12.1</v>
       </c>
       <c r="M81">
-        <v>36.17969004</v>
+        <v>36.63766080000001</v>
       </c>
       <c r="N81">
-        <v>-24.07969004</v>
+        <v>-24.5376608</v>
       </c>
       <c r="O81">
-        <v>-5.7791256096</v>
+        <v>-5.889038592000001</v>
       </c>
       <c r="P81">
-        <v>-18.3005644304</v>
+        <v>-18.648622208</v>
       </c>
       <c r="Q81">
-        <v>-9.300564430400001</v>
+        <v>-9.648622208000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.32307055943688</v>
+        <v>0.336934087408724</v>
       </c>
       <c r="T81">
-        <v>5.700974534342512</v>
+        <v>5.986023261059637</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08026602761906912</v>
+        <v>0.07926270227383075</v>
       </c>
       <c r="W81">
-        <v>0.2168732706874235</v>
+        <v>0.2171098548038307</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3344417817461214</v>
+        <v>0.3302612594742949</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2410747013248093</v>
+        <v>0.2429747013248094</v>
       </c>
       <c r="C82">
-        <v>-75.69878257536953</v>
+        <v>-78.15051403367411</v>
       </c>
       <c r="D82">
-        <v>52.87721742463047</v>
+        <v>52.3676859663259</v>
       </c>
       <c r="E82">
-        <v>149.256</v>
+        <v>151.1982</v>
       </c>
       <c r="F82">
-        <v>155.376</v>
+        <v>157.3182</v>
       </c>
       <c r="G82">
         <v>26.8</v>
@@ -8017,37 +8017,37 @@
         <v>12.1</v>
       </c>
       <c r="M82">
-        <v>36.63766080000001</v>
+        <v>37.09563156000001</v>
       </c>
       <c r="N82">
-        <v>-24.5376608</v>
+        <v>-24.99563156000001</v>
       </c>
       <c r="O82">
-        <v>-5.889038592000001</v>
+        <v>-5.998951574400001</v>
       </c>
       <c r="P82">
-        <v>-18.648622208</v>
+        <v>-18.9966799856</v>
       </c>
       <c r="Q82">
-        <v>-9.648622208000003</v>
+        <v>-9.996679985600004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.336934087408724</v>
+        <v>0.3522569341144464</v>
       </c>
       <c r="T82">
-        <v>5.986023261059637</v>
+        <v>6.301077116904883</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07926270227383075</v>
+        <v>0.0782841503939069</v>
       </c>
       <c r="W82">
-        <v>0.2171098548038307</v>
+        <v>0.2173405973371167</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3302612594742949</v>
+        <v>0.3261839599746121</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2429747013248094</v>
+        <v>0.2448747013248094</v>
       </c>
       <c r="C83">
-        <v>-78.15051403367411</v>
+        <v>-80.59251939655483</v>
       </c>
       <c r="D83">
-        <v>52.3676859663259</v>
+        <v>51.86788060344517</v>
       </c>
       <c r="E83">
-        <v>151.1982</v>
+        <v>153.1404</v>
       </c>
       <c r="F83">
-        <v>157.3182</v>
+        <v>159.2604</v>
       </c>
       <c r="G83">
         <v>26.8</v>
@@ -8099,37 +8099,37 @@
         <v>12.1</v>
       </c>
       <c r="M83">
-        <v>37.09563156000001</v>
+        <v>37.55360232</v>
       </c>
       <c r="N83">
-        <v>-24.99563156000001</v>
+        <v>-25.45360232</v>
       </c>
       <c r="O83">
-        <v>-5.998951574400001</v>
+        <v>-6.1088645568</v>
       </c>
       <c r="P83">
-        <v>-18.9966799856</v>
+        <v>-19.3447377632</v>
       </c>
       <c r="Q83">
-        <v>-9.996679985600004</v>
+        <v>-10.3447377632</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3522569341144464</v>
+        <v>0.3692823193430267</v>
       </c>
       <c r="T83">
-        <v>6.301077116904883</v>
+        <v>6.651136956732932</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0782841503939069</v>
+        <v>0.07732946563300562</v>
       </c>
       <c r="W83">
-        <v>0.2173405973371167</v>
+        <v>0.2175657120037373</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3261839599746121</v>
+        <v>0.32220610680419</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2448747013248094</v>
+        <v>0.2467747013248094</v>
       </c>
       <c r="C84">
-        <v>-80.59251939655483</v>
+        <v>-83.02507451337762</v>
       </c>
       <c r="D84">
-        <v>51.86788060344517</v>
+        <v>51.3775254866224</v>
       </c>
       <c r="E84">
-        <v>153.1404</v>
+        <v>155.0826</v>
       </c>
       <c r="F84">
-        <v>159.2604</v>
+        <v>161.2026</v>
       </c>
       <c r="G84">
         <v>26.8</v>
@@ -8181,37 +8181,37 @@
         <v>12.1</v>
       </c>
       <c r="M84">
-        <v>37.55360232</v>
+        <v>38.01157308000001</v>
       </c>
       <c r="N84">
-        <v>-25.45360232</v>
+        <v>-25.91157308</v>
       </c>
       <c r="O84">
-        <v>-6.1088645568</v>
+        <v>-6.2187775392</v>
       </c>
       <c r="P84">
-        <v>-19.3447377632</v>
+        <v>-19.6927955408</v>
       </c>
       <c r="Q84">
-        <v>-10.3447377632</v>
+        <v>-10.6927955408</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3692823193430267</v>
+        <v>0.3883106910690872</v>
       </c>
       <c r="T84">
-        <v>6.651136956732932</v>
+        <v>7.042380307128988</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07732946563300562</v>
+        <v>0.07639778532417422</v>
       </c>
       <c r="W84">
-        <v>0.2175657120037373</v>
+        <v>0.2177854022205597</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.32220610680419</v>
+        <v>0.3183241055173925</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2467747013248094</v>
+        <v>0.2486747013248093</v>
       </c>
       <c r="C85">
-        <v>-83.02507451337762</v>
+        <v>-85.44844489976448</v>
       </c>
       <c r="D85">
-        <v>51.3775254866224</v>
+        <v>50.89635510023552</v>
       </c>
       <c r="E85">
-        <v>155.0826</v>
+        <v>157.0248</v>
       </c>
       <c r="F85">
-        <v>161.2026</v>
+        <v>163.1448</v>
       </c>
       <c r="G85">
         <v>26.8</v>
@@ -8263,37 +8263,37 @@
         <v>12.1</v>
       </c>
       <c r="M85">
-        <v>38.01157308000001</v>
+        <v>38.46954384</v>
       </c>
       <c r="N85">
-        <v>-25.91157308</v>
+        <v>-26.36954384</v>
       </c>
       <c r="O85">
-        <v>-6.2187775392</v>
+        <v>-6.3286905216</v>
       </c>
       <c r="P85">
-        <v>-19.6927955408</v>
+        <v>-20.0408533184</v>
       </c>
       <c r="Q85">
-        <v>-10.6927955408</v>
+        <v>-11.0408533184</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3883106910690872</v>
+        <v>0.4097176092609051</v>
       </c>
       <c r="T85">
-        <v>7.042380307128988</v>
+        <v>7.48252907632455</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07639778532417422</v>
+        <v>0.07548828787983881</v>
       </c>
       <c r="W85">
-        <v>0.2177854022205597</v>
+        <v>0.217999861717934</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3183241055173925</v>
+        <v>0.3145345328326618</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2486747013248093</v>
+        <v>0.2505747013248094</v>
       </c>
       <c r="C86">
-        <v>-85.44844489976448</v>
+        <v>-87.8628862170015</v>
       </c>
       <c r="D86">
-        <v>50.89635510023552</v>
+        <v>50.42411378299848</v>
       </c>
       <c r="E86">
-        <v>157.0248</v>
+        <v>158.967</v>
       </c>
       <c r="F86">
-        <v>163.1448</v>
+        <v>165.087</v>
       </c>
       <c r="G86">
         <v>26.8</v>
@@ -8345,37 +8345,37 @@
         <v>12.1</v>
       </c>
       <c r="M86">
-        <v>38.46954384</v>
+        <v>38.9275146</v>
       </c>
       <c r="N86">
-        <v>-26.36954384</v>
+        <v>-26.8275146</v>
       </c>
       <c r="O86">
-        <v>-6.3286905216</v>
+        <v>-6.438603504</v>
       </c>
       <c r="P86">
-        <v>-20.0408533184</v>
+        <v>-20.388911096</v>
       </c>
       <c r="Q86">
-        <v>-11.0408533184</v>
+        <v>-11.388911096</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4097176092609049</v>
+        <v>0.4339787832116319</v>
       </c>
       <c r="T86">
-        <v>7.482529076324544</v>
+        <v>7.981364348079516</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07548828787983881</v>
+        <v>0.07460019037537012</v>
       </c>
       <c r="W86">
-        <v>0.217999861717934</v>
+        <v>0.2182092751094877</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3145345328326618</v>
+        <v>0.3108341265640422</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2505747013248094</v>
+        <v>0.2524747013248094</v>
       </c>
       <c r="C87">
-        <v>-87.8628862170015</v>
+        <v>-90.2686447250026</v>
       </c>
       <c r="D87">
-        <v>50.42411378299848</v>
+        <v>49.9605552749974</v>
       </c>
       <c r="E87">
-        <v>158.967</v>
+        <v>160.9092</v>
       </c>
       <c r="F87">
-        <v>165.087</v>
+        <v>167.0292</v>
       </c>
       <c r="G87">
         <v>26.8</v>
@@ -8427,37 +8427,37 @@
         <v>12.1</v>
       </c>
       <c r="M87">
-        <v>38.9275146</v>
+        <v>39.38548536</v>
       </c>
       <c r="N87">
-        <v>-26.8275146</v>
+        <v>-27.28548536</v>
       </c>
       <c r="O87">
-        <v>-6.438603504</v>
+        <v>-6.548516486400001</v>
       </c>
       <c r="P87">
-        <v>-20.388911096</v>
+        <v>-20.7369688736</v>
       </c>
       <c r="Q87">
-        <v>-11.388911096</v>
+        <v>-11.7369688736</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4339787832116319</v>
+        <v>0.4617058391553199</v>
       </c>
       <c r="T87">
-        <v>7.981364348079516</v>
+        <v>8.551461801513767</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07460019037537012</v>
+        <v>0.07373274630123791</v>
       </c>
       <c r="W87">
-        <v>0.2182092751094877</v>
+        <v>0.2184138184221681</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3108341265640422</v>
+        <v>0.307219776255158</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2524747013248094</v>
+        <v>0.2543747013248093</v>
       </c>
       <c r="C88">
-        <v>-90.2686447250026</v>
+        <v>-92.66595771051595</v>
       </c>
       <c r="D88">
-        <v>49.9605552749974</v>
+        <v>49.50544228948404</v>
       </c>
       <c r="E88">
-        <v>160.9092</v>
+        <v>162.8514</v>
       </c>
       <c r="F88">
-        <v>167.0292</v>
+        <v>168.9714</v>
       </c>
       <c r="G88">
         <v>26.8</v>
@@ -8509,37 +8509,37 @@
         <v>12.1</v>
       </c>
       <c r="M88">
-        <v>39.38548536</v>
+        <v>39.84345612</v>
       </c>
       <c r="N88">
-        <v>-27.28548536</v>
+        <v>-27.74345612</v>
       </c>
       <c r="O88">
-        <v>-6.548516486400001</v>
+        <v>-6.658429468799999</v>
       </c>
       <c r="P88">
-        <v>-20.7369688736</v>
+        <v>-21.0850266512</v>
       </c>
       <c r="Q88">
-        <v>-11.7369688736</v>
+        <v>-12.0850266512</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4617058391553199</v>
+        <v>0.4936985960134214</v>
       </c>
       <c r="T88">
-        <v>8.551461801513767</v>
+        <v>9.209266555476363</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07373274630123791</v>
+        <v>0.07288524347018921</v>
       </c>
       <c r="W88">
-        <v>0.2184138184221681</v>
+        <v>0.2186136595897294</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.307219776255158</v>
+        <v>0.3036885144591217</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2543747013248093</v>
+        <v>0.2562747013248093</v>
       </c>
       <c r="C89">
-        <v>-92.66595771051595</v>
+        <v>-95.05505389213764</v>
       </c>
       <c r="D89">
-        <v>49.50544228948404</v>
+        <v>49.05854610786237</v>
       </c>
       <c r="E89">
-        <v>162.8514</v>
+        <v>164.7936</v>
       </c>
       <c r="F89">
-        <v>168.9714</v>
+        <v>170.9136</v>
       </c>
       <c r="G89">
         <v>26.8</v>
@@ -8591,37 +8591,37 @@
         <v>12.1</v>
       </c>
       <c r="M89">
-        <v>39.84345612</v>
+        <v>40.30142688</v>
       </c>
       <c r="N89">
-        <v>-27.74345612</v>
+        <v>-28.20142688</v>
       </c>
       <c r="O89">
-        <v>-6.658429468799999</v>
+        <v>-6.7683424512</v>
       </c>
       <c r="P89">
-        <v>-21.0850266512</v>
+        <v>-21.4330844288</v>
       </c>
       <c r="Q89">
-        <v>-12.0850266512</v>
+        <v>-12.4330844288</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4936985960134214</v>
+        <v>0.5310234790145399</v>
       </c>
       <c r="T89">
-        <v>9.209266555476363</v>
+        <v>9.976705435099396</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07288524347018921</v>
+        <v>0.07205700206711887</v>
       </c>
       <c r="W89">
-        <v>0.2186136595897294</v>
+        <v>0.2188089589125734</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3036885144591217</v>
+        <v>0.3002375086129954</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2562747013248093</v>
+        <v>0.2581747013248094</v>
       </c>
       <c r="C90">
-        <v>-95.05505389213764</v>
+        <v>-97.43615380358415</v>
       </c>
       <c r="D90">
-        <v>49.05854610786237</v>
+        <v>48.61964619641584</v>
       </c>
       <c r="E90">
-        <v>164.7936</v>
+        <v>166.7358</v>
       </c>
       <c r="F90">
-        <v>170.9136</v>
+        <v>172.8558</v>
       </c>
       <c r="G90">
         <v>26.8</v>
@@ -8673,37 +8673,37 @@
         <v>12.1</v>
       </c>
       <c r="M90">
-        <v>40.30142688</v>
+        <v>40.75939764</v>
       </c>
       <c r="N90">
-        <v>-28.20142688</v>
+        <v>-28.65939763999999</v>
       </c>
       <c r="O90">
-        <v>-6.7683424512</v>
+        <v>-6.878255433599999</v>
       </c>
       <c r="P90">
-        <v>-21.4330844288</v>
+        <v>-21.78114220639999</v>
       </c>
       <c r="Q90">
-        <v>-12.4330844288</v>
+        <v>-12.78114220639999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5310234790145399</v>
+        <v>0.5751347043794981</v>
       </c>
       <c r="T90">
-        <v>9.976705435099396</v>
+        <v>10.88367865647207</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07205700206711887</v>
+        <v>0.07124737283040969</v>
       </c>
       <c r="W90">
-        <v>0.2188089589125734</v>
+        <v>0.2189998694865894</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3002375086129954</v>
+        <v>0.2968640534600403</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2581747013248094</v>
+        <v>0.2600747013248094</v>
       </c>
       <c r="C91">
-        <v>-97.43615380358415</v>
+        <v>-99.80947015657422</v>
       </c>
       <c r="D91">
-        <v>48.61964619641584</v>
+        <v>48.18852984342578</v>
       </c>
       <c r="E91">
-        <v>166.7358</v>
+        <v>168.678</v>
       </c>
       <c r="F91">
-        <v>172.8558</v>
+        <v>174.798</v>
       </c>
       <c r="G91">
         <v>26.8</v>
@@ -8755,37 +8755,37 @@
         <v>12.1</v>
       </c>
       <c r="M91">
-        <v>40.75939764</v>
+        <v>41.21736840000001</v>
       </c>
       <c r="N91">
-        <v>-28.65939763999999</v>
+        <v>-29.1173684</v>
       </c>
       <c r="O91">
-        <v>-6.878255433599999</v>
+        <v>-6.988168416000001</v>
       </c>
       <c r="P91">
-        <v>-21.78114220639999</v>
+        <v>-22.129199984</v>
       </c>
       <c r="Q91">
-        <v>-12.78114220639999</v>
+        <v>-13.129199984</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5751347043794981</v>
+        <v>0.6280681748174479</v>
       </c>
       <c r="T91">
-        <v>10.88367865647207</v>
+        <v>11.97204652211927</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07124737283040969</v>
+        <v>0.07045573535451623</v>
       </c>
       <c r="W91">
-        <v>0.2189998694865894</v>
+        <v>0.2191865376034051</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2968640534600403</v>
+        <v>0.2935655639771509</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2600747013248094</v>
+        <v>0.2619747013248094</v>
       </c>
       <c r="C92">
-        <v>-99.80947015657422</v>
+        <v>-102.1752081845738</v>
       </c>
       <c r="D92">
-        <v>48.18852984342578</v>
+        <v>47.76499181542618</v>
       </c>
       <c r="E92">
-        <v>168.678</v>
+        <v>170.6202</v>
       </c>
       <c r="F92">
-        <v>174.798</v>
+        <v>176.7402</v>
       </c>
       <c r="G92">
         <v>26.8</v>
@@ -8837,37 +8837,37 @@
         <v>12.1</v>
       </c>
       <c r="M92">
-        <v>41.21736840000001</v>
+        <v>41.67533916000001</v>
       </c>
       <c r="N92">
-        <v>-29.1173684</v>
+        <v>-29.57533916000001</v>
       </c>
       <c r="O92">
-        <v>-6.988168416000001</v>
+        <v>-7.098081398400002</v>
       </c>
       <c r="P92">
-        <v>-22.129199984</v>
+        <v>-22.4772577616</v>
       </c>
       <c r="Q92">
-        <v>-13.129199984</v>
+        <v>-13.4772577616</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6280681748174479</v>
+        <v>0.6927646386860534</v>
       </c>
       <c r="T92">
-        <v>11.97204652211927</v>
+        <v>13.30227391346586</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07045573535451623</v>
+        <v>0.0696814965044666</v>
       </c>
       <c r="W92">
-        <v>0.2191865376034051</v>
+        <v>0.2193691031242468</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2935655639771509</v>
+        <v>0.2903395687686108</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2619747013248094</v>
+        <v>0.2638747013248094</v>
       </c>
       <c r="C93">
-        <v>-102.1752081845738</v>
+        <v>-104.5335659685716</v>
       </c>
       <c r="D93">
-        <v>47.76499181542618</v>
+        <v>47.3488340314284</v>
       </c>
       <c r="E93">
-        <v>170.6202</v>
+        <v>172.5624</v>
       </c>
       <c r="F93">
-        <v>176.7402</v>
+        <v>178.6824</v>
       </c>
       <c r="G93">
         <v>26.8</v>
@@ -8919,37 +8919,37 @@
         <v>12.1</v>
       </c>
       <c r="M93">
-        <v>41.67533916000001</v>
+        <v>42.13330992</v>
       </c>
       <c r="N93">
-        <v>-29.57533916000001</v>
+        <v>-30.03330992</v>
       </c>
       <c r="O93">
-        <v>-7.098081398400002</v>
+        <v>-7.2079943808</v>
       </c>
       <c r="P93">
-        <v>-22.4772577616</v>
+        <v>-22.8253155392</v>
       </c>
       <c r="Q93">
-        <v>-13.4772577616</v>
+        <v>-13.8253155392</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6927646386860534</v>
+        <v>0.7736352185218102</v>
       </c>
       <c r="T93">
-        <v>13.30227391346586</v>
+        <v>14.9650581526491</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0696814965044666</v>
+        <v>0.06892408893376588</v>
       </c>
       <c r="W93">
-        <v>0.2193691031242468</v>
+        <v>0.219547699829418</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2903395687686108</v>
+        <v>0.2871837038906911</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2638747013248094</v>
+        <v>0.2657747013248094</v>
       </c>
       <c r="C94">
-        <v>-104.5335659685716</v>
+        <v>-106.8847347459715</v>
       </c>
       <c r="D94">
-        <v>47.3488340314284</v>
+        <v>46.93986525402851</v>
       </c>
       <c r="E94">
-        <v>172.5624</v>
+        <v>174.5046</v>
       </c>
       <c r="F94">
-        <v>178.6824</v>
+        <v>180.6246</v>
       </c>
       <c r="G94">
         <v>26.8</v>
@@ -9001,37 +9001,37 @@
         <v>12.1</v>
       </c>
       <c r="M94">
-        <v>42.13330992</v>
+        <v>42.59128068</v>
       </c>
       <c r="N94">
-        <v>-30.03330992</v>
+        <v>-30.49128068</v>
       </c>
       <c r="O94">
-        <v>-7.2079943808</v>
+        <v>-7.317907363200001</v>
       </c>
       <c r="P94">
-        <v>-22.8253155392</v>
+        <v>-23.1733733168</v>
       </c>
       <c r="Q94">
-        <v>-13.8253155392</v>
+        <v>-14.1733733168</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7736352185218102</v>
+        <v>0.8776116783106404</v>
       </c>
       <c r="T94">
-        <v>14.9650581526491</v>
+        <v>17.10292360302754</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06892408893376588</v>
+        <v>0.06818296969791893</v>
       </c>
       <c r="W94">
-        <v>0.219547699829418</v>
+        <v>0.2197224557452307</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2871837038906911</v>
+        <v>0.2840957070746623</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2657747013248094</v>
+        <v>0.2676747013248094</v>
       </c>
       <c r="C95">
-        <v>-106.8847347459715</v>
+        <v>-109.2288992036141</v>
       </c>
       <c r="D95">
-        <v>46.93986525402851</v>
+        <v>46.53790079638585</v>
       </c>
       <c r="E95">
-        <v>174.5046</v>
+        <v>176.4468</v>
       </c>
       <c r="F95">
-        <v>180.6246</v>
+        <v>182.5668</v>
       </c>
       <c r="G95">
         <v>26.8</v>
@@ -9083,37 +9083,37 @@
         <v>12.1</v>
       </c>
       <c r="M95">
-        <v>42.59128068</v>
+        <v>43.04925144</v>
       </c>
       <c r="N95">
-        <v>-30.49128068</v>
+        <v>-30.94925144</v>
       </c>
       <c r="O95">
-        <v>-7.317907363200001</v>
+        <v>-7.427820345599999</v>
       </c>
       <c r="P95">
-        <v>-23.1733733168</v>
+        <v>-23.5214310944</v>
       </c>
       <c r="Q95">
-        <v>-14.1733733168</v>
+        <v>-14.5214310944</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8776116783106404</v>
+        <v>1.016246958029081</v>
       </c>
       <c r="T95">
-        <v>17.10292360302754</v>
+        <v>19.95341087019881</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06818296969791893</v>
+        <v>0.06745761895645172</v>
       </c>
       <c r="W95">
-        <v>0.2197224557452307</v>
+        <v>0.2198934934500687</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2840957070746623</v>
+        <v>0.2810734123185489</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2676747013248094</v>
+        <v>0.2695747013248094</v>
       </c>
       <c r="C96">
-        <v>-109.2288992036141</v>
+        <v>-111.5662377558708</v>
       </c>
       <c r="D96">
-        <v>46.53790079638585</v>
+        <v>46.14276224412926</v>
       </c>
       <c r="E96">
-        <v>176.4468</v>
+        <v>178.389</v>
       </c>
       <c r="F96">
-        <v>182.5668</v>
+        <v>184.509</v>
       </c>
       <c r="G96">
         <v>26.8</v>
@@ -9165,37 +9165,37 @@
         <v>12.1</v>
       </c>
       <c r="M96">
-        <v>43.04925144</v>
+        <v>43.50722220000001</v>
       </c>
       <c r="N96">
-        <v>-30.94925144</v>
+        <v>-31.40722220000001</v>
       </c>
       <c r="O96">
-        <v>-7.427820345599999</v>
+        <v>-7.537733328000002</v>
       </c>
       <c r="P96">
-        <v>-23.5214310944</v>
+        <v>-23.86948887200001</v>
       </c>
       <c r="Q96">
-        <v>-14.5214310944</v>
+        <v>-14.86948887200001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.016246958029081</v>
+        <v>1.210336349634898</v>
       </c>
       <c r="T96">
-        <v>19.95341087019881</v>
+        <v>23.94409304423858</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06745761895645172</v>
+        <v>0.0667475387569101</v>
       </c>
       <c r="W96">
-        <v>0.2198934934500687</v>
+        <v>0.2200609303611206</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2810734123185489</v>
+        <v>0.2781147448204587</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2695747013248094</v>
+        <v>0.2714747013248094</v>
       </c>
       <c r="C97">
-        <v>-111.5662377558708</v>
+        <v>-113.8969228086887</v>
       </c>
       <c r="D97">
-        <v>46.14276224412926</v>
+        <v>45.75427719131132</v>
       </c>
       <c r="E97">
-        <v>178.389</v>
+        <v>180.3312</v>
       </c>
       <c r="F97">
-        <v>184.509</v>
+        <v>186.4512</v>
       </c>
       <c r="G97">
         <v>26.8</v>
@@ -9247,37 +9247,37 @@
         <v>12.1</v>
       </c>
       <c r="M97">
-        <v>43.50722220000001</v>
+        <v>43.96519296</v>
       </c>
       <c r="N97">
-        <v>-31.40722220000001</v>
+        <v>-31.86519296</v>
       </c>
       <c r="O97">
-        <v>-7.537733328000002</v>
+        <v>-7.6476463104</v>
       </c>
       <c r="P97">
-        <v>-23.86948887200001</v>
+        <v>-24.2175466496</v>
       </c>
       <c r="Q97">
-        <v>-14.86948887200001</v>
+        <v>-15.2175466496</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.210336349634898</v>
+        <v>1.501470437043623</v>
       </c>
       <c r="T97">
-        <v>23.94409304423858</v>
+        <v>29.93011630529824</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0667475387569101</v>
+        <v>0.06605225189485897</v>
       </c>
       <c r="W97">
-        <v>0.2200609303611206</v>
+        <v>0.2202248790031923</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2781147448204587</v>
+        <v>0.275217716228579</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2714747013248094</v>
+        <v>0.2733747013248093</v>
       </c>
       <c r="C98">
-        <v>-113.8969228086887</v>
+        <v>-116.2211210104106</v>
       </c>
       <c r="D98">
-        <v>45.75427719131132</v>
+        <v>45.37227898958935</v>
       </c>
       <c r="E98">
-        <v>180.3312</v>
+        <v>182.2734</v>
       </c>
       <c r="F98">
-        <v>186.4512</v>
+        <v>188.3934</v>
       </c>
       <c r="G98">
         <v>26.8</v>
@@ -9329,37 +9329,37 @@
         <v>12.1</v>
       </c>
       <c r="M98">
-        <v>43.96519296</v>
+        <v>44.42316372</v>
       </c>
       <c r="N98">
-        <v>-31.86519296</v>
+        <v>-32.32316372</v>
       </c>
       <c r="O98">
-        <v>-7.6476463104</v>
+        <v>-7.757559292799999</v>
       </c>
       <c r="P98">
-        <v>-24.2175466496</v>
+        <v>-24.5656044272</v>
       </c>
       <c r="Q98">
-        <v>-15.2175466496</v>
+        <v>-15.5656044272</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.501470437043619</v>
+        <v>1.986693916058158</v>
       </c>
       <c r="T98">
-        <v>29.93011630529816</v>
+        <v>39.90682174039755</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06605225189485897</v>
+        <v>0.06537130084439652</v>
       </c>
       <c r="W98">
-        <v>0.2202248790031923</v>
+        <v>0.2203854472608913</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.275217716228579</v>
+        <v>0.2723804201849854</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2733747013248093</v>
+        <v>0.2752747013248094</v>
       </c>
       <c r="C99">
-        <v>-116.2211210104106</v>
+        <v>-118.5389934901329</v>
       </c>
       <c r="D99">
-        <v>45.37227898958935</v>
+        <v>44.99660650986707</v>
       </c>
       <c r="E99">
-        <v>182.2734</v>
+        <v>184.2156</v>
       </c>
       <c r="F99">
-        <v>188.3934</v>
+        <v>190.3356</v>
       </c>
       <c r="G99">
         <v>26.8</v>
@@ -9411,37 +9411,37 @@
         <v>12.1</v>
       </c>
       <c r="M99">
-        <v>44.42316372</v>
+        <v>44.88113448</v>
       </c>
       <c r="N99">
-        <v>-32.32316372</v>
+        <v>-32.78113448</v>
       </c>
       <c r="O99">
-        <v>-7.757559292799999</v>
+        <v>-7.867472275199999</v>
       </c>
       <c r="P99">
-        <v>-24.5656044272</v>
+        <v>-24.9136622048</v>
       </c>
       <c r="Q99">
-        <v>-15.5656044272</v>
+        <v>-15.9136622048</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.986693916058158</v>
+        <v>2.957140874087237</v>
       </c>
       <c r="T99">
-        <v>39.90682174039755</v>
+        <v>59.86023261059632</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06537130084439652</v>
+        <v>0.06470424675414757</v>
       </c>
       <c r="W99">
-        <v>0.2203854472608913</v>
+        <v>0.220542738615372</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2723804201849854</v>
+        <v>0.2696010281422815</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2752747013248094</v>
+        <v>0.2771747013248094</v>
       </c>
       <c r="C100">
-        <v>-118.5389934901329</v>
+        <v>-120.8506960843198</v>
       </c>
       <c r="D100">
-        <v>44.99660650986707</v>
+        <v>44.62710391568013</v>
       </c>
       <c r="E100">
-        <v>184.2156</v>
+        <v>186.1578</v>
       </c>
       <c r="F100">
-        <v>190.3356</v>
+        <v>192.2778</v>
       </c>
       <c r="G100">
         <v>26.8</v>
@@ -9493,37 +9493,37 @@
         <v>12.1</v>
       </c>
       <c r="M100">
-        <v>44.88113448</v>
+        <v>45.33910523999999</v>
       </c>
       <c r="N100">
-        <v>-32.78113448</v>
+        <v>-33.23910523999999</v>
       </c>
       <c r="O100">
-        <v>-7.867472275199999</v>
+        <v>-7.977385257599998</v>
       </c>
       <c r="P100">
-        <v>-24.9136622048</v>
+        <v>-25.2617199824</v>
       </c>
       <c r="Q100">
-        <v>-15.9136622048</v>
+        <v>-16.2617199824</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.957140874087237</v>
+        <v>5.868481748174474</v>
       </c>
       <c r="T100">
-        <v>59.86023261059632</v>
+        <v>119.7204652211926</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06470424675414757</v>
+        <v>0.06405066850410568</v>
       </c>
       <c r="W100">
-        <v>0.220542738615372</v>
+        <v>0.2206968523667319</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2696010281422815</v>
+        <v>0.2668777854337736</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2771747013248094</v>
-      </c>
-      <c r="C101">
-        <v>-120.8506960843198</v>
-      </c>
-      <c r="D101">
-        <v>44.62710391568013</v>
-      </c>
-      <c r="E101">
-        <v>186.1578</v>
-      </c>
-      <c r="F101">
-        <v>192.2778</v>
-      </c>
-      <c r="G101">
-        <v>26.8</v>
-      </c>
-      <c r="H101">
-        <v>188.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>21.1</v>
-      </c>
-      <c r="K101">
-        <v>9</v>
-      </c>
-      <c r="L101">
-        <v>12.1</v>
-      </c>
-      <c r="M101">
-        <v>45.33910523999999</v>
-      </c>
-      <c r="N101">
-        <v>-33.23910523999999</v>
-      </c>
-      <c r="O101">
-        <v>-7.977385257599998</v>
-      </c>
-      <c r="P101">
-        <v>-25.2617199824</v>
-      </c>
-      <c r="Q101">
-        <v>-16.2617199824</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.868481748174474</v>
-      </c>
-      <c r="T101">
-        <v>119.7204652211926</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06405066850410568</v>
-      </c>
-      <c r="W101">
-        <v>0.2206968523667319</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2668777854337736</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
